--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3">
-        <v>28546400</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3">
-        <v>18741200</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3">
-        <v>14609500</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="D8" s="3">
+        <v>29136100</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>28627900</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3">
+        <v>18794800</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
+        <v>14651300</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
         <v>11756000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>10311300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>9862300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>11817800</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>13838500</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>13949800</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>13909700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>11989100</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -951,8 +957,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1052,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1277,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,100 +1372,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-900600</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-866900</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-835500</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="D15" s="3">
+        <v>-919400</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-903100</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-869400</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-837800</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="3">
         <v>-921500</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
         <v>-841100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>-854800</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>-814900</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3">
         <v>-889600</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>-852900</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>-611600</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-534700</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>342900</v>
+        <v>24844600</v>
       </c>
       <c r="E17" s="3">
-        <v>22751400</v>
+        <v>343800</v>
       </c>
       <c r="F17" s="3">
-        <v>197500</v>
+        <v>22816400</v>
       </c>
       <c r="G17" s="3">
-        <v>12542600</v>
+        <v>198000</v>
       </c>
       <c r="H17" s="3">
-        <v>494800</v>
+        <v>12578400</v>
       </c>
       <c r="I17" s="3">
-        <v>8662600</v>
+        <v>496200</v>
       </c>
       <c r="J17" s="3">
+        <v>8687400</v>
+      </c>
+      <c r="K17" s="3">
         <v>608700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5863900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>211100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5462500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>292000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6073200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>537600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8143600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>925900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8100700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>403000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8077200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>315800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8066200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>292400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5419700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>228400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>574500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>736000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="3">
-        <v>5795000</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3">
-        <v>6198600</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3">
-        <v>5946900</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>4291500</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
+        <v>5811500</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3">
+        <v>6216300</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
+        <v>5963900</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>5892100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>4848800</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>3789100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>3674200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>5737800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>5872600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>5843500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>6569300</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,100 +1726,104 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-2511800</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2059300</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-5486800</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="D20" s="3">
+        <v>-2004300</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-2519000</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-2065200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-5502500</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-703600</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1812,74 +1848,77 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3">
         <v>11090300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>7409700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>5908300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>6270200</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>6188900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>6010500</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,192 +2009,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1287900</v>
+        <v>2287200</v>
       </c>
       <c r="E23" s="3">
-        <v>3283200</v>
+        <v>1291600</v>
       </c>
       <c r="F23" s="3">
-        <v>1540700</v>
+        <v>3292600</v>
       </c>
       <c r="G23" s="3">
-        <v>4139300</v>
+        <v>1545100</v>
       </c>
       <c r="H23" s="3">
-        <v>2244900</v>
+        <v>4151100</v>
       </c>
       <c r="I23" s="3">
-        <v>460000</v>
+        <v>2251300</v>
       </c>
       <c r="J23" s="3">
+        <v>461400</v>
+      </c>
+      <c r="K23" s="3">
         <v>1468000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5188500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2671800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3437400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1301300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2160400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1514300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-835600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-275500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2904500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1749300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3202200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1312200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3419800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2149900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3542100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>677000</v>
+        <v>1007600</v>
       </c>
       <c r="E24" s="3">
-        <v>817000</v>
+        <v>679000</v>
       </c>
       <c r="F24" s="3">
-        <v>355900</v>
+        <v>819300</v>
       </c>
       <c r="G24" s="3">
-        <v>893000</v>
+        <v>356900</v>
       </c>
       <c r="H24" s="3">
-        <v>400400</v>
+        <v>895500</v>
       </c>
       <c r="I24" s="3">
-        <v>716100</v>
+        <v>401500</v>
       </c>
       <c r="J24" s="3">
+        <v>718100</v>
+      </c>
+      <c r="K24" s="3">
         <v>361300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1094900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>752800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>726800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>299400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>590500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>484700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>667600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-51900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>722600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>476500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>758800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>305000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>637600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>597000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>840000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>406300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>515000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>775300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>456600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>610900</v>
+        <v>1279600</v>
       </c>
       <c r="E26" s="3">
-        <v>2466200</v>
+        <v>612600</v>
       </c>
       <c r="F26" s="3">
-        <v>1184800</v>
+        <v>2473300</v>
       </c>
       <c r="G26" s="3">
-        <v>3246300</v>
+        <v>1188200</v>
       </c>
       <c r="H26" s="3">
-        <v>1844500</v>
+        <v>3255600</v>
       </c>
       <c r="I26" s="3">
-        <v>-256100</v>
+        <v>1849800</v>
       </c>
       <c r="J26" s="3">
+        <v>-256800</v>
+      </c>
+      <c r="K26" s="3">
         <v>1106700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4093600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1919000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2710600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1001900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1569900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1029600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-223600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2181900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1272800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2443400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1007200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2782200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1552900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2702200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>141100</v>
+        <v>375400</v>
       </c>
       <c r="E27" s="3">
-        <v>1508200</v>
+        <v>141500</v>
       </c>
       <c r="F27" s="3">
-        <v>764900</v>
+        <v>1512500</v>
       </c>
       <c r="G27" s="3">
-        <v>2383700</v>
+        <v>767100</v>
       </c>
       <c r="H27" s="3">
-        <v>1432200</v>
+        <v>2390600</v>
       </c>
       <c r="I27" s="3">
-        <v>-1050300</v>
+        <v>1436300</v>
       </c>
       <c r="J27" s="3">
+        <v>-1053300</v>
+      </c>
+      <c r="K27" s="3">
         <v>763800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3368300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1584100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2056800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>708900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1038300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>762900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-547600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1346000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>825600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1627000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>623200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1915100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1239400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1957700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>821300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>885300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>939100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>727800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2579,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2614,8 +2674,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2511800</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2059300</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>5486800</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="D32" s="3">
+        <v>2004300</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>2519000</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2065200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
+        <v>5502500</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>703600</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>1411400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>1628800</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>4509800</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>2833300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>2670400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>2423800</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>3027200</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>141100</v>
+        <v>375400</v>
       </c>
       <c r="E33" s="3">
-        <v>1508200</v>
+        <v>141500</v>
       </c>
       <c r="F33" s="3">
-        <v>764900</v>
+        <v>1512500</v>
       </c>
       <c r="G33" s="3">
-        <v>2383700</v>
+        <v>767100</v>
       </c>
       <c r="H33" s="3">
-        <v>1432200</v>
+        <v>2390600</v>
       </c>
       <c r="I33" s="3">
-        <v>-1050300</v>
+        <v>1436300</v>
       </c>
       <c r="J33" s="3">
+        <v>-1053300</v>
+      </c>
+      <c r="K33" s="3">
         <v>763800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3368300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1584100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2056800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>708900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1038300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>762900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-547600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1346000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>825600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1627000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>623200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1915100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1239400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1957700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>821300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>885300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>939100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>727800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>141100</v>
+        <v>375400</v>
       </c>
       <c r="E35" s="3">
-        <v>1508200</v>
+        <v>141500</v>
       </c>
       <c r="F35" s="3">
-        <v>764900</v>
+        <v>1512500</v>
       </c>
       <c r="G35" s="3">
-        <v>2383700</v>
+        <v>767100</v>
       </c>
       <c r="H35" s="3">
-        <v>1432200</v>
+        <v>2390600</v>
       </c>
       <c r="I35" s="3">
-        <v>-1050300</v>
+        <v>1436300</v>
       </c>
       <c r="J35" s="3">
+        <v>-1053300</v>
+      </c>
+      <c r="K35" s="3">
         <v>763800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3368300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1584100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2056800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>708900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1038300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>762900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-547600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1346000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>825600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1627000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>623200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1915100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1239400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1957700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>821300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>885300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>939100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>727800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,192 +3416,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>348727700</v>
+        <v>300691000</v>
       </c>
       <c r="E41" s="3">
-        <v>294928000</v>
+        <v>349724000</v>
       </c>
       <c r="F41" s="3">
-        <v>327852300</v>
+        <v>295770600</v>
       </c>
       <c r="G41" s="3">
-        <v>353452900</v>
+        <v>328789000</v>
       </c>
       <c r="H41" s="3">
-        <v>302248500</v>
+        <v>354462700</v>
       </c>
       <c r="I41" s="3">
-        <v>258401400</v>
+        <v>303112000</v>
       </c>
       <c r="J41" s="3">
+        <v>259139700</v>
+      </c>
+      <c r="K41" s="3">
         <v>330465000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>244721500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>261336700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>217609400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>254792900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>209707300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>225571000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>202919100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>220891500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>163996600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>194104600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>171349700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>197168400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>164605300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>178050000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>144180600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>64577000</v>
+        <v>618543500</v>
       </c>
       <c r="E42" s="3">
-        <v>641305500</v>
+        <v>64761500</v>
       </c>
       <c r="F42" s="3">
-        <v>63143700</v>
+        <v>643137800</v>
       </c>
       <c r="G42" s="3">
-        <v>557364500</v>
+        <v>63324200</v>
       </c>
       <c r="H42" s="3">
-        <v>55637700</v>
+        <v>558957000</v>
       </c>
       <c r="I42" s="3">
-        <v>493317000</v>
+        <v>55796700</v>
       </c>
       <c r="J42" s="3">
+        <v>494726400</v>
+      </c>
+      <c r="K42" s="3">
         <v>36272600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>427770700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>35223200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>530635700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>34644200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>467173200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>38143900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>525051700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>37311100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>529056200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>42058800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>579304100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>31521100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>513271000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>25238900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>488778000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3607,8 +3699,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3699,8 +3794,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3791,8 +3889,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3883,284 +3984,296 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>225700</v>
+        <v>247000</v>
       </c>
       <c r="E47" s="3">
-        <v>226800</v>
+        <v>226300</v>
       </c>
       <c r="F47" s="3">
-        <v>169300</v>
+        <v>227400</v>
       </c>
       <c r="G47" s="3">
-        <v>158400</v>
+        <v>169700</v>
       </c>
       <c r="H47" s="3">
+        <v>158900</v>
+      </c>
+      <c r="I47" s="3">
+        <v>125100</v>
+      </c>
+      <c r="J47" s="3">
+        <v>120800</v>
+      </c>
+      <c r="K47" s="3">
         <v>124800</v>
       </c>
-      <c r="I47" s="3">
-        <v>120400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>124800</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>103000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>102300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>101600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>109000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>99700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>103800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>115600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>129800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>130700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>317300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>285900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>311000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>294500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>737700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>719200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>768600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>785400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>897600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>817900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>64021500</v>
+        <v>66062900</v>
       </c>
       <c r="E48" s="3">
-        <v>62425500</v>
+        <v>64204400</v>
       </c>
       <c r="F48" s="3">
-        <v>37385800</v>
+        <v>62603800</v>
       </c>
       <c r="G48" s="3">
-        <v>36844400</v>
+        <v>37492700</v>
       </c>
       <c r="H48" s="3">
-        <v>35857100</v>
+        <v>36949700</v>
       </c>
       <c r="I48" s="3">
-        <v>35387300</v>
+        <v>35959500</v>
       </c>
       <c r="J48" s="3">
+        <v>35488400</v>
+      </c>
+      <c r="K48" s="3">
         <v>34870800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34656500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33577700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32571600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32128300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30009800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30711500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32522200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34099900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>33024900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>36724000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>31480500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>34927800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>31643800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28864100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>28039600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5693000</v>
+        <v>5385000</v>
       </c>
       <c r="E49" s="3">
-        <v>5992500</v>
+        <v>5709300</v>
       </c>
       <c r="F49" s="3">
-        <v>4105600</v>
+        <v>6009600</v>
       </c>
       <c r="G49" s="3">
-        <v>4102400</v>
+        <v>4117400</v>
       </c>
       <c r="H49" s="3">
-        <v>4116500</v>
+        <v>4114100</v>
       </c>
       <c r="I49" s="3">
-        <v>4116500</v>
+        <v>4128300</v>
       </c>
       <c r="J49" s="3">
+        <v>4128300</v>
+      </c>
+      <c r="K49" s="3">
         <v>4056800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4055600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>4042600</v>
       </c>
       <c r="N49" s="3">
         <v>4042600</v>
       </c>
       <c r="O49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="P49" s="3">
         <v>4033500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4199300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4412700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5337300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8160200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5747700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8087800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5457100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5502900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5385200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5351700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,100 +4459,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6393900</v>
+        <v>5934500</v>
       </c>
       <c r="E52" s="3">
-        <v>7943300</v>
+        <v>6412200</v>
       </c>
       <c r="F52" s="3">
-        <v>5929500</v>
+        <v>7966000</v>
       </c>
       <c r="G52" s="3">
-        <v>10014600</v>
+        <v>5946500</v>
       </c>
       <c r="H52" s="3">
-        <v>4889000</v>
+        <v>10043200</v>
       </c>
       <c r="I52" s="3">
-        <v>4197900</v>
+        <v>4903000</v>
       </c>
       <c r="J52" s="3">
+        <v>4209900</v>
+      </c>
+      <c r="K52" s="3">
         <v>5059400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4181400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5058200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4621300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5898400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4095300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8964300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8922600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10436300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10796200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12949400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16134300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>20145200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>22854800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11710700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10751600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1735400000</v>
+        <v>1690956400</v>
       </c>
       <c r="E54" s="3">
-        <v>1712596600</v>
+        <v>1740358300</v>
       </c>
       <c r="F54" s="3">
-        <v>1685682000</v>
+        <v>1717489700</v>
       </c>
       <c r="G54" s="3">
-        <v>1611116500</v>
+        <v>1690498300</v>
       </c>
       <c r="H54" s="3">
-        <v>1728992000</v>
+        <v>1615719700</v>
       </c>
       <c r="I54" s="3">
-        <v>1669407000</v>
+        <v>1733932000</v>
       </c>
       <c r="J54" s="3">
+        <v>1674176800</v>
+      </c>
+      <c r="K54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,25 +4816,26 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3">
-        <v>27546000</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
-        <v>24129300</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>33246900</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3">
+        <v>27624700</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
+        <v>24198300</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
@@ -4713,74 +4843,77 @@
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>23345000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>21322900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>19225900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>22898200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3">
         <v>25886100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3">
         <v>30259400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3">
         <v>26338500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="3">
         <v>24286700</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4793,11 +4926,11 @@
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G58" s="3">
-        <v>74557900</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3">
+        <v>74771000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
@@ -4805,14 +4938,14 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3">
         <v>121369300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4871,25 +5004,28 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
-        <v>2397900</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2831900</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>2792100</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2404700</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2839900</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
@@ -4897,74 +5033,77 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>2985600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>3007900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>2016700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>1815300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>2759800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>2592800</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>2834200</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
         <v>2290400</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5055,192 +5194,201 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>183184900</v>
+        <v>52307100</v>
       </c>
       <c r="E61" s="3">
-        <v>45859700</v>
+        <v>183708300</v>
       </c>
       <c r="F61" s="3">
-        <v>167397100</v>
+        <v>45990700</v>
       </c>
       <c r="G61" s="3">
-        <v>44143200</v>
+        <v>167875300</v>
       </c>
       <c r="H61" s="3">
-        <v>154927200</v>
+        <v>44269300</v>
       </c>
       <c r="I61" s="3">
-        <v>41294000</v>
+        <v>155369800</v>
       </c>
       <c r="J61" s="3">
+        <v>41412000</v>
+      </c>
+      <c r="K61" s="3">
         <v>164361200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>56119500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>160479600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>53062900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>173731000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>54638600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>166334900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>59718600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>187453200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>61859900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>177461900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43963200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>168898700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>54097600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>140870100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>41046500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9050000</v>
+        <v>9074800</v>
       </c>
       <c r="E62" s="3">
-        <v>9922300</v>
+        <v>9075800</v>
       </c>
       <c r="F62" s="3">
-        <v>6946200</v>
+        <v>9950700</v>
       </c>
       <c r="G62" s="3">
-        <v>11960000</v>
+        <v>6966000</v>
       </c>
       <c r="H62" s="3">
-        <v>7206600</v>
+        <v>11994100</v>
       </c>
       <c r="I62" s="3">
-        <v>7077500</v>
+        <v>7227200</v>
       </c>
       <c r="J62" s="3">
+        <v>7097700</v>
+      </c>
+      <c r="K62" s="3">
         <v>7302100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6968600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6783400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5772400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6505600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5943500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6783700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7107300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6967700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8322500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12323400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15154400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17011200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>19181900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12837100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11585000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1661536500</v>
+        <v>1619169000</v>
       </c>
       <c r="E66" s="3">
-        <v>1638809000</v>
+        <v>1666283700</v>
       </c>
       <c r="F66" s="3">
-        <v>1611091500</v>
+        <v>1643491300</v>
       </c>
       <c r="G66" s="3">
-        <v>1538454100</v>
+        <v>1615694700</v>
       </c>
       <c r="H66" s="3">
-        <v>1657044600</v>
+        <v>1542849600</v>
       </c>
       <c r="I66" s="3">
-        <v>1599335600</v>
+        <v>1661779000</v>
       </c>
       <c r="J66" s="3">
+        <v>1603905100</v>
+      </c>
+      <c r="K66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +5989,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>39554800</v>
+        <v>38501300</v>
       </c>
       <c r="E72" s="3">
-        <v>39334500</v>
+        <v>39667800</v>
       </c>
       <c r="F72" s="3">
-        <v>40265400</v>
+        <v>39446900</v>
       </c>
       <c r="G72" s="3">
-        <v>39389800</v>
+        <v>40380500</v>
       </c>
       <c r="H72" s="3">
-        <v>38495800</v>
+        <v>39502400</v>
       </c>
       <c r="I72" s="3">
-        <v>36929100</v>
+        <v>38605800</v>
       </c>
       <c r="J72" s="3">
+        <v>37034600</v>
+      </c>
+      <c r="K72" s="3">
         <v>40266500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>39322500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>37390000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>35140400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>34342700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31761200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>32832900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>33673100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36431500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38298100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>39706800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37388300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39071500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38096500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35056600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33541700</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>73863500</v>
+        <v>71787400</v>
       </c>
       <c r="E76" s="3">
-        <v>73787600</v>
+        <v>74074600</v>
       </c>
       <c r="F76" s="3">
-        <v>74590500</v>
+        <v>73998400</v>
       </c>
       <c r="G76" s="3">
-        <v>72662500</v>
+        <v>74803600</v>
       </c>
       <c r="H76" s="3">
-        <v>71947400</v>
+        <v>72870100</v>
       </c>
       <c r="I76" s="3">
-        <v>70071500</v>
+        <v>72153000</v>
       </c>
       <c r="J76" s="3">
+        <v>70271700</v>
+      </c>
+      <c r="K76" s="3">
         <v>71449400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>70539100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>68531800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>66797900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>66569400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>61549600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>62889500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66173500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>70660200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>74162100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>78050200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>73515600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>73961000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>72187700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>66621000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>64737000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>141100</v>
+        <v>375400</v>
       </c>
       <c r="E81" s="3">
-        <v>1508200</v>
+        <v>141500</v>
       </c>
       <c r="F81" s="3">
-        <v>764900</v>
+        <v>1512500</v>
       </c>
       <c r="G81" s="3">
-        <v>2383700</v>
+        <v>767100</v>
       </c>
       <c r="H81" s="3">
-        <v>1432200</v>
+        <v>2390600</v>
       </c>
       <c r="I81" s="3">
-        <v>-1050300</v>
+        <v>1436300</v>
       </c>
       <c r="J81" s="3">
+        <v>-1053300</v>
+      </c>
+      <c r="K81" s="3">
         <v>763800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3368300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1584100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2056800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>708900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1038300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>762900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-547600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1346000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>825600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1627000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>623200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1915100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1239400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1957700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>821300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>885300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>939100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>727800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +6981,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>5901800</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
         <v>5249300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
         <v>3003700</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
         <v>3068100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
         <v>2769200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2468300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
         <v>22772600</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>80580900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>8778900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>3392700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3">
         <v>21205800</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,100 +7681,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6744000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5123000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3099000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6480000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3026000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,8 +8096,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7921,11 +8154,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7933,11 +8166,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -7945,19 +8178,22 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,174 +8474,180 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>2160400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
         <v>178600</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>2184600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
         <v>-900200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>2335200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3">
         <v>778700</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
         <v>845800</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3">
         <v>947500</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1513000</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8416,96 +8664,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3">
         <v>9436000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3">
         <v>73274000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>4652100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>3339800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3">
         <v>14449100</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,217 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>29136100</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
-        <v>28627900</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
-        <v>18794800</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>28937900</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>28433200</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3">
+        <v>18666900</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
         <v>14651300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
         <v>11756000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
         <v>10311300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>9862300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>11817800</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
         <v>13838500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W8" s="3">
         <v>13949800</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="3">
         <v>13909700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -960,8 +966,11 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1055,8 +1064,11 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,103 +1394,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>-919400</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-903100</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-869400</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-913200</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3">
+        <v>-897000</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-863500</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="3">
         <v>-837800</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
         <v>-921500</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3">
         <v>-841100</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-854800</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3">
         <v>-814900</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15" s="3">
         <v>-889600</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" s="3">
         <v>-852900</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-611600</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>24844600</v>
+        <v>432300</v>
       </c>
       <c r="E17" s="3">
-        <v>343800</v>
+        <v>24675600</v>
       </c>
       <c r="F17" s="3">
-        <v>22816400</v>
+        <v>341500</v>
       </c>
       <c r="G17" s="3">
-        <v>198000</v>
+        <v>22661200</v>
       </c>
       <c r="H17" s="3">
-        <v>12578400</v>
+        <v>196700</v>
       </c>
       <c r="I17" s="3">
-        <v>496200</v>
+        <v>12492900</v>
       </c>
       <c r="J17" s="3">
+        <v>492800</v>
+      </c>
+      <c r="K17" s="3">
         <v>8687400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>608700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5863900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>211100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5462500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>292000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6073200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>537600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8143600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>925900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8100700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>403000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8077200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>315800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8066200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>292400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>228400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>574500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>736000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>4291500</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3">
-        <v>5811500</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3">
-        <v>6216300</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4262300</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3">
+        <v>5772000</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3">
+        <v>6174000</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>5963900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>5892100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>4848800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>3789100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>3674200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>5737800</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>5872600</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>5843500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,123 +1759,127 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-2004300</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2519000</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2065200</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1990600</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-2501800</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2051200</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>-703600</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
+      <c r="E21" s="3">
+        <v>10603800</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
+      <c r="G21" s="3">
+        <v>6533900</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
+      <c r="I21" s="3">
+        <v>9896000</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
@@ -1851,74 +1887,77 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>11090300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>7409700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>5908300</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>6270200</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>6188900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2012,198 +2051,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2287200</v>
+        <v>1280600</v>
       </c>
       <c r="E23" s="3">
-        <v>1291600</v>
+        <v>2271600</v>
       </c>
       <c r="F23" s="3">
-        <v>3292600</v>
+        <v>1282800</v>
       </c>
       <c r="G23" s="3">
-        <v>1545100</v>
+        <v>3270200</v>
       </c>
       <c r="H23" s="3">
-        <v>4151100</v>
+        <v>1534600</v>
       </c>
       <c r="I23" s="3">
-        <v>2251300</v>
+        <v>4122900</v>
       </c>
       <c r="J23" s="3">
+        <v>2236000</v>
+      </c>
+      <c r="K23" s="3">
         <v>461400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1468000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5188500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2671800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3437400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1301300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2160400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1514300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-835600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-275500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2904500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1749300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3202200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1312200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3419800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2149900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1007600</v>
+        <v>296100</v>
       </c>
       <c r="E24" s="3">
-        <v>679000</v>
+        <v>1000700</v>
       </c>
       <c r="F24" s="3">
-        <v>819300</v>
+        <v>674400</v>
       </c>
       <c r="G24" s="3">
-        <v>356900</v>
+        <v>813800</v>
       </c>
       <c r="H24" s="3">
-        <v>895500</v>
+        <v>354500</v>
       </c>
       <c r="I24" s="3">
-        <v>401500</v>
+        <v>889400</v>
       </c>
       <c r="J24" s="3">
+        <v>398800</v>
+      </c>
+      <c r="K24" s="3">
         <v>718100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>361300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1094900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>752800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>726800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>299400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>590500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>484700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>667600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-51900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>722600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>476500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>758800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>305000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>637600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>597000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>840000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>406300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>515000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>775300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>456600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1279600</v>
+        <v>984500</v>
       </c>
       <c r="E26" s="3">
-        <v>612600</v>
+        <v>1270900</v>
       </c>
       <c r="F26" s="3">
-        <v>2473300</v>
+        <v>608400</v>
       </c>
       <c r="G26" s="3">
-        <v>1188200</v>
+        <v>2456400</v>
       </c>
       <c r="H26" s="3">
-        <v>3255600</v>
+        <v>1180100</v>
       </c>
       <c r="I26" s="3">
-        <v>1849800</v>
+        <v>3233500</v>
       </c>
       <c r="J26" s="3">
+        <v>1837200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-256800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1106700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4093600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1919000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2710600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1001900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1569900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1029600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-223600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2181900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1272800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2443400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1007200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2782200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1552900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>375400</v>
+        <v>555500</v>
       </c>
       <c r="E27" s="3">
-        <v>141500</v>
+        <v>372800</v>
       </c>
       <c r="F27" s="3">
-        <v>1512500</v>
+        <v>140500</v>
       </c>
       <c r="G27" s="3">
-        <v>767100</v>
+        <v>1502200</v>
       </c>
       <c r="H27" s="3">
-        <v>2390600</v>
+        <v>761900</v>
       </c>
       <c r="I27" s="3">
-        <v>1436300</v>
+        <v>2374300</v>
       </c>
       <c r="J27" s="3">
+        <v>1426500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>763800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3368300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1584100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2056800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>708900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1038300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>762900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-547600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1346000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>825600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1627000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>623200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1915100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1239400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>821300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>885300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>939100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>727800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,8 +2639,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2677,8 +2737,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>2004300</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2519000</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2065200</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1990600</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2501800</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2051200</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>5502500</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>703600</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>1411400</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1628800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>4509800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>2833300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>2670400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3">
         <v>2423800</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>375400</v>
+        <v>555500</v>
       </c>
       <c r="E33" s="3">
-        <v>141500</v>
+        <v>372800</v>
       </c>
       <c r="F33" s="3">
-        <v>1512500</v>
+        <v>140500</v>
       </c>
       <c r="G33" s="3">
-        <v>767100</v>
+        <v>1502200</v>
       </c>
       <c r="H33" s="3">
-        <v>2390600</v>
+        <v>761900</v>
       </c>
       <c r="I33" s="3">
-        <v>1436300</v>
+        <v>2374300</v>
       </c>
       <c r="J33" s="3">
+        <v>1426500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>763800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3368300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1584100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2056800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>708900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1038300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>762900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-547600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1346000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>825600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1627000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>623200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1915100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1239400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>821300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>885300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>939100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>727800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>375400</v>
+        <v>555500</v>
       </c>
       <c r="E35" s="3">
-        <v>141500</v>
+        <v>372800</v>
       </c>
       <c r="F35" s="3">
-        <v>1512500</v>
+        <v>140500</v>
       </c>
       <c r="G35" s="3">
-        <v>767100</v>
+        <v>1502200</v>
       </c>
       <c r="H35" s="3">
-        <v>2390600</v>
+        <v>761900</v>
       </c>
       <c r="I35" s="3">
-        <v>1436300</v>
+        <v>2374300</v>
       </c>
       <c r="J35" s="3">
+        <v>1426500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>763800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3368300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1584100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2056800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>708900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1038300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>762900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-547600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1346000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>825600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1627000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>623200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1915100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1239400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>821300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>885300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>939100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>727800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,198 +3502,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>300691000</v>
+        <v>324974100</v>
       </c>
       <c r="E41" s="3">
-        <v>349724000</v>
+        <v>298646000</v>
       </c>
       <c r="F41" s="3">
-        <v>295770600</v>
+        <v>347345600</v>
       </c>
       <c r="G41" s="3">
-        <v>328789000</v>
+        <v>293759100</v>
       </c>
       <c r="H41" s="3">
-        <v>354462700</v>
+        <v>326553000</v>
       </c>
       <c r="I41" s="3">
-        <v>303112000</v>
+        <v>352052100</v>
       </c>
       <c r="J41" s="3">
+        <v>301050600</v>
+      </c>
+      <c r="K41" s="3">
         <v>259139700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>330465000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>244721500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>261336700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>217609400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>254792900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>209707300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>225571000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>202919100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>220891500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>163996600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>194104600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>171349700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>197168400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>164605300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>178050000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>618543500</v>
+        <v>40864500</v>
       </c>
       <c r="E42" s="3">
-        <v>64761500</v>
+        <v>614336900</v>
       </c>
       <c r="F42" s="3">
-        <v>643137800</v>
+        <v>64321100</v>
       </c>
       <c r="G42" s="3">
-        <v>63324200</v>
+        <v>638763900</v>
       </c>
       <c r="H42" s="3">
-        <v>558957000</v>
+        <v>62893500</v>
       </c>
       <c r="I42" s="3">
-        <v>55796700</v>
+        <v>555155600</v>
       </c>
       <c r="J42" s="3">
+        <v>55417200</v>
+      </c>
+      <c r="K42" s="3">
         <v>494726400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36272600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>427770700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>35223200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>530635700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>34644200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>467173200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>38143900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>525051700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>37311100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>529056200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>42058800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>579304100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>31521100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>513271000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>25238900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3702,8 +3794,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3797,8 +3892,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3892,8 +3990,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3987,293 +4088,305 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>247000</v>
+        <v>246400</v>
       </c>
       <c r="E47" s="3">
-        <v>226300</v>
+        <v>245300</v>
       </c>
       <c r="F47" s="3">
-        <v>227400</v>
+        <v>224800</v>
       </c>
       <c r="G47" s="3">
-        <v>169700</v>
+        <v>225900</v>
       </c>
       <c r="H47" s="3">
-        <v>158900</v>
+        <v>168600</v>
       </c>
       <c r="I47" s="3">
-        <v>125100</v>
+        <v>157800</v>
       </c>
       <c r="J47" s="3">
+        <v>124300</v>
+      </c>
+      <c r="K47" s="3">
         <v>120800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>124800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>103000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>102300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>101600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>109000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>99700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>103800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>115600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>129800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>130700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>317300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>285900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>311000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>294500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>737700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>719200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>768600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>785400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>897600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>817900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>66062900</v>
+        <v>65843800</v>
       </c>
       <c r="E48" s="3">
-        <v>64204400</v>
+        <v>65613600</v>
       </c>
       <c r="F48" s="3">
-        <v>62603800</v>
+        <v>63767800</v>
       </c>
       <c r="G48" s="3">
-        <v>37492700</v>
+        <v>62178100</v>
       </c>
       <c r="H48" s="3">
-        <v>36949700</v>
+        <v>37237700</v>
       </c>
       <c r="I48" s="3">
-        <v>35959500</v>
+        <v>36698400</v>
       </c>
       <c r="J48" s="3">
+        <v>35715000</v>
+      </c>
+      <c r="K48" s="3">
         <v>35488400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34870800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34656500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33577700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32571600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32128300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30009800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30711500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32522200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34099900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>33024900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36724000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>31480500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>34927800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>31643800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>28864100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5385000</v>
+        <v>5345100</v>
       </c>
       <c r="E49" s="3">
-        <v>5709300</v>
+        <v>5348400</v>
       </c>
       <c r="F49" s="3">
-        <v>6009600</v>
+        <v>5670400</v>
       </c>
       <c r="G49" s="3">
-        <v>4117400</v>
+        <v>5968700</v>
       </c>
       <c r="H49" s="3">
-        <v>4114100</v>
+        <v>4089400</v>
       </c>
       <c r="I49" s="3">
+        <v>4086100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>4100200</v>
+      </c>
+      <c r="K49" s="3">
         <v>4128300</v>
       </c>
-      <c r="J49" s="3">
-        <v>4128300</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4056800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4055600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>4042600</v>
       </c>
       <c r="O49" s="3">
         <v>4042600</v>
       </c>
       <c r="P49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="Q49" s="3">
         <v>4033500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4199300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4412700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5337300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8160200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5747700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8087800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5457100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5502900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5385200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,103 +4578,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5934500</v>
+        <v>35799300</v>
       </c>
       <c r="E52" s="3">
-        <v>6412200</v>
+        <v>5894100</v>
       </c>
       <c r="F52" s="3">
-        <v>7966000</v>
+        <v>6368600</v>
       </c>
       <c r="G52" s="3">
-        <v>5946500</v>
+        <v>7911800</v>
       </c>
       <c r="H52" s="3">
-        <v>10043200</v>
+        <v>5906000</v>
       </c>
       <c r="I52" s="3">
-        <v>4903000</v>
+        <v>9974900</v>
       </c>
       <c r="J52" s="3">
+        <v>4869600</v>
+      </c>
+      <c r="K52" s="3">
         <v>4209900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5059400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4181400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5058200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4621300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5898400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4095300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8964300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8922600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10436300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10796200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12949400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16134300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>20145200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>22854800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11710700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1690956400</v>
+        <v>1718919300</v>
       </c>
       <c r="E54" s="3">
-        <v>1740358300</v>
+        <v>1679456400</v>
       </c>
       <c r="F54" s="3">
-        <v>1717489700</v>
+        <v>1728522400</v>
       </c>
       <c r="G54" s="3">
-        <v>1690498300</v>
+        <v>1705809300</v>
       </c>
       <c r="H54" s="3">
-        <v>1615719700</v>
+        <v>1679001500</v>
       </c>
       <c r="I54" s="3">
-        <v>1733932000</v>
+        <v>1604731400</v>
       </c>
       <c r="J54" s="3">
+        <v>1722139800</v>
+      </c>
+      <c r="K54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,28 +4946,29 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>33246900</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3">
-        <v>27624700</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3">
-        <v>24198300</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
+        <v>33020800</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3">
+        <v>27436800</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
+        <v>24033700</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
@@ -4846,74 +4976,77 @@
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>23345000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>21322900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3">
         <v>19225900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="3">
         <v>22898200</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3">
         <v>25886100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W57" s="3">
         <v>30259400</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y57" s="3">
         <v>26338500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4929,11 +5062,11 @@
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H58" s="3">
-        <v>74771000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3">
+        <v>74262500</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>4</v>
@@ -4941,14 +5074,14 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3">
         <v>121369300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -5007,28 +5140,31 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>2792100</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2404700</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2839900</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2773100</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2388300</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2820600</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
@@ -5036,74 +5172,77 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>2985600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>3007900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2016700</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S59" s="3">
         <v>1815300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3">
         <v>2759800</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
         <v>2592800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3">
         <v>2834200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5197,198 +5336,207 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>52307100</v>
+        <v>197135900</v>
       </c>
       <c r="E61" s="3">
-        <v>183708300</v>
+        <v>51951400</v>
       </c>
       <c r="F61" s="3">
-        <v>45990700</v>
+        <v>182458900</v>
       </c>
       <c r="G61" s="3">
-        <v>167875300</v>
+        <v>45677900</v>
       </c>
       <c r="H61" s="3">
-        <v>44269300</v>
+        <v>166733600</v>
       </c>
       <c r="I61" s="3">
-        <v>155369800</v>
+        <v>43968300</v>
       </c>
       <c r="J61" s="3">
+        <v>154313200</v>
+      </c>
+      <c r="K61" s="3">
         <v>41412000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164361200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>56119500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>160479600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>53062900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>173731000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>54638600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>166334900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>59718600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>187453200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>61859900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>177461900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>43963200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>168898700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>54097600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>140870100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9074800</v>
+        <v>26651100</v>
       </c>
       <c r="E62" s="3">
-        <v>9075800</v>
+        <v>9013000</v>
       </c>
       <c r="F62" s="3">
-        <v>9950700</v>
+        <v>9014100</v>
       </c>
       <c r="G62" s="3">
-        <v>6966000</v>
+        <v>9883000</v>
       </c>
       <c r="H62" s="3">
-        <v>11994100</v>
+        <v>6918600</v>
       </c>
       <c r="I62" s="3">
-        <v>7227200</v>
+        <v>11912600</v>
       </c>
       <c r="J62" s="3">
+        <v>7178000</v>
+      </c>
+      <c r="K62" s="3">
         <v>7097700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7302100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6968600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6783400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5772400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6505600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5943500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6783700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7107300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6967700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8322500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12323400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15154400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17011200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19181900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12837100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1619169000</v>
+        <v>1646142800</v>
       </c>
       <c r="E66" s="3">
-        <v>1666283700</v>
+        <v>1608157200</v>
       </c>
       <c r="F66" s="3">
-        <v>1643491300</v>
+        <v>1654951600</v>
       </c>
       <c r="G66" s="3">
-        <v>1615694700</v>
+        <v>1632314100</v>
       </c>
       <c r="H66" s="3">
-        <v>1542849600</v>
+        <v>1604706600</v>
       </c>
       <c r="I66" s="3">
-        <v>1661779000</v>
+        <v>1532357000</v>
       </c>
       <c r="J66" s="3">
+        <v>1650477500</v>
+      </c>
+      <c r="K66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>38501300</v>
+        <v>38771200</v>
       </c>
       <c r="E72" s="3">
-        <v>39667800</v>
+        <v>38239500</v>
       </c>
       <c r="F72" s="3">
-        <v>39446900</v>
+        <v>39398000</v>
       </c>
       <c r="G72" s="3">
-        <v>40380500</v>
+        <v>39178600</v>
       </c>
       <c r="H72" s="3">
-        <v>39502400</v>
+        <v>40105900</v>
       </c>
       <c r="I72" s="3">
-        <v>38605800</v>
+        <v>39233700</v>
       </c>
       <c r="J72" s="3">
+        <v>38343200</v>
+      </c>
+      <c r="K72" s="3">
         <v>37034600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40266500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>39322500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>37390000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>35140400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>34342700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>31761200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>32832900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>33673100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36431500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38298100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>39706800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>37388300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>39071500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38096500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35056600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>71787400</v>
+        <v>72776500</v>
       </c>
       <c r="E76" s="3">
-        <v>74074600</v>
+        <v>71299200</v>
       </c>
       <c r="F76" s="3">
-        <v>73998400</v>
+        <v>73570800</v>
       </c>
       <c r="G76" s="3">
-        <v>74803600</v>
+        <v>73495200</v>
       </c>
       <c r="H76" s="3">
-        <v>72870100</v>
+        <v>74294900</v>
       </c>
       <c r="I76" s="3">
-        <v>72153000</v>
+        <v>72374500</v>
       </c>
       <c r="J76" s="3">
+        <v>71662300</v>
+      </c>
+      <c r="K76" s="3">
         <v>70271700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71449400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>70539100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>68531800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>66797900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>66569400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>61549600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62889500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>66173500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70660200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>74162100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>78050200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>73515600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>73961000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>72187700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>66621000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>375400</v>
+        <v>555500</v>
       </c>
       <c r="E81" s="3">
-        <v>141500</v>
+        <v>372800</v>
       </c>
       <c r="F81" s="3">
-        <v>1512500</v>
+        <v>140500</v>
       </c>
       <c r="G81" s="3">
-        <v>767100</v>
+        <v>1502200</v>
       </c>
       <c r="H81" s="3">
-        <v>2390600</v>
+        <v>761900</v>
       </c>
       <c r="I81" s="3">
-        <v>1436300</v>
+        <v>2374300</v>
       </c>
       <c r="J81" s="3">
+        <v>1426500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>763800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3368300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1584100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2056800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>708900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1038300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>762900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-547600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1346000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>825600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1627000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>623200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1915100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1239400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>821300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>885300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>939100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>727800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,103 +7179,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+        <v>8332200</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+        <v>3263700</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
+        <v>5791500</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>5901800</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5249300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3">
         <v>3003700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W83" s="3">
         <v>3068100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
         <v>2769200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
+        <v>40443000</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
+        <v>23996900</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L89" s="3">
+        <v>42246700</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>22772600</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
         <v>80580900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3">
         <v>8778900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W89" s="3">
         <v>3392700</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3">
         <v>21205800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,8 +7901,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7706,79 +7926,82 @@
         <v>-3440000</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+        <v>-13047300</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+        <v>-4232000</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3">
+        <v>-9727400</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,8 +8329,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8157,11 +8390,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -8169,11 +8402,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8181,19 +8414,22 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,180 +8719,186 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+        <v>-4216900</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+        <v>-2482400</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L100" s="3">
+        <v>-231300</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>2160400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3">
         <v>178600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W100" s="3">
         <v>2184600</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-900200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
+        <v>-2507200</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
+        <v>-2625000</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L101" s="3">
+        <v>2544000</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3">
         <v>2335200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U101" s="3">
         <v>778700</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W101" s="3">
         <v>845800</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y101" s="3">
         <v>947500</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8667,99 +8915,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
+        <v>20671600</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
+        <v>14657500</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L102" s="3">
+        <v>34820200</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3">
         <v>9436000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3">
         <v>73274000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3">
         <v>4652100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3">
         <v>3339800</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3">
         <v>14449100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,223 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3">
-        <v>28937900</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3">
-        <v>28433200</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3">
-        <v>18666900</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="D8" s="3">
+        <v>31552200</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>29658200</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3">
+        <v>29141000</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
+        <v>19131600</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
         <v>14651300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>11756000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>10311300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>9862300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>11817800</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>13838500</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>13949800</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>13909700</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -969,8 +975,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1067,8 +1076,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1315,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,106 +1416,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-913200</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-897000</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-863500</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="D15" s="3">
+        <v>-900500</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-935900</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-919300</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-885000</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="3">
         <v>-837800</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
         <v>-921500</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>-841100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>-854800</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3">
         <v>-814900</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>-889600</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>-852900</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-611600</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>432300</v>
+        <v>27046500</v>
       </c>
       <c r="E17" s="3">
-        <v>24675600</v>
+        <v>443000</v>
       </c>
       <c r="F17" s="3">
-        <v>341500</v>
+        <v>25289800</v>
       </c>
       <c r="G17" s="3">
-        <v>22661200</v>
+        <v>350000</v>
       </c>
       <c r="H17" s="3">
-        <v>196700</v>
+        <v>23225300</v>
       </c>
       <c r="I17" s="3">
-        <v>12492900</v>
+        <v>201600</v>
       </c>
       <c r="J17" s="3">
+        <v>12803900</v>
+      </c>
+      <c r="K17" s="3">
         <v>492800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8687400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>608700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5863900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>211100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5462500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>292000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6073200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>537600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8143600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>925900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8100700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>403000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8077200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>315800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8066200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>292400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>228400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>574500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>736000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="3">
-        <v>4262300</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3">
-        <v>5772000</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3">
-        <v>6174000</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>4505700</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4368400</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3">
+        <v>5915700</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
+        <v>6327700</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>5963900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>5892100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>4848800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>3789100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>3674200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>5737800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>5872600</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>5843500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,129 +1792,133 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1990600</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2501800</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2051200</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="D20" s="3">
+        <v>-1273700</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-2040200</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-2564100</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-2102200</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-703600</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3">
-        <v>10603800</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3">
-        <v>6533900</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3">
-        <v>9896000</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>8834200</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3">
+        <v>10867800</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3">
+        <v>6696500</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3">
+        <v>10142300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1890,74 +1926,77 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>11090300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>7409700</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>5908300</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>6270200</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>6188900</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2054,204 +2093,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1280600</v>
+        <v>3232000</v>
       </c>
       <c r="E23" s="3">
-        <v>2271600</v>
+        <v>1312500</v>
       </c>
       <c r="F23" s="3">
-        <v>1282800</v>
+        <v>2328200</v>
       </c>
       <c r="G23" s="3">
-        <v>3270200</v>
+        <v>1314700</v>
       </c>
       <c r="H23" s="3">
-        <v>1534600</v>
+        <v>3351600</v>
       </c>
       <c r="I23" s="3">
-        <v>4122900</v>
+        <v>1572800</v>
       </c>
       <c r="J23" s="3">
+        <v>4225500</v>
+      </c>
+      <c r="K23" s="3">
         <v>2236000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>461400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1468000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5188500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2671800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3437400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1301300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2160400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1514300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-835600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-275500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2904500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1749300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3202200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1312200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3419800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>296100</v>
+        <v>723300</v>
       </c>
       <c r="E24" s="3">
-        <v>1000700</v>
+        <v>303500</v>
       </c>
       <c r="F24" s="3">
-        <v>674400</v>
+        <v>1025600</v>
       </c>
       <c r="G24" s="3">
-        <v>813800</v>
+        <v>691100</v>
       </c>
       <c r="H24" s="3">
-        <v>354500</v>
+        <v>834000</v>
       </c>
       <c r="I24" s="3">
-        <v>889400</v>
+        <v>363300</v>
       </c>
       <c r="J24" s="3">
+        <v>911600</v>
+      </c>
+      <c r="K24" s="3">
         <v>398800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>718100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>361300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1094900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>752800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>726800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>299400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>590500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>484700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>667600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-51900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>722600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>476500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>758800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>305000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>637600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>597000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>840000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>406300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>515000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>775300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>456600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>984500</v>
+        <v>2508700</v>
       </c>
       <c r="E26" s="3">
-        <v>1270900</v>
+        <v>1009000</v>
       </c>
       <c r="F26" s="3">
-        <v>608400</v>
+        <v>1302500</v>
       </c>
       <c r="G26" s="3">
-        <v>2456400</v>
+        <v>623600</v>
       </c>
       <c r="H26" s="3">
-        <v>1180100</v>
+        <v>2517600</v>
       </c>
       <c r="I26" s="3">
-        <v>3233500</v>
+        <v>1209500</v>
       </c>
       <c r="J26" s="3">
+        <v>3313900</v>
+      </c>
+      <c r="K26" s="3">
         <v>1837200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-256800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1106700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4093600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1919000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2710600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1001900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1569900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1029600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-223600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2181900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1272800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2443400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1007200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2782200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>555500</v>
+        <v>1591600</v>
       </c>
       <c r="E27" s="3">
-        <v>372800</v>
+        <v>569300</v>
       </c>
       <c r="F27" s="3">
-        <v>140500</v>
+        <v>382100</v>
       </c>
       <c r="G27" s="3">
-        <v>1502200</v>
+        <v>144000</v>
       </c>
       <c r="H27" s="3">
-        <v>761900</v>
+        <v>1539600</v>
       </c>
       <c r="I27" s="3">
-        <v>2374300</v>
+        <v>780900</v>
       </c>
       <c r="J27" s="3">
+        <v>2433400</v>
+      </c>
+      <c r="K27" s="3">
         <v>1426500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>763800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3368300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1584100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2056800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>708900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1038300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>762900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-547600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1346000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>825600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1627000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>623200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1915100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>821300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>885300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>939100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>727800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2740,8 +2800,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1990600</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2501800</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2051200</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="D32" s="3">
+        <v>1273700</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>2040200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2564100</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2102200</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>5502500</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>703600</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>1411400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>1628800</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>4509800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>2833300</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>2670400</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2423800</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>555500</v>
+        <v>1591600</v>
       </c>
       <c r="E33" s="3">
-        <v>372800</v>
+        <v>569300</v>
       </c>
       <c r="F33" s="3">
-        <v>140500</v>
+        <v>382100</v>
       </c>
       <c r="G33" s="3">
-        <v>1502200</v>
+        <v>144000</v>
       </c>
       <c r="H33" s="3">
-        <v>761900</v>
+        <v>1539600</v>
       </c>
       <c r="I33" s="3">
-        <v>2374300</v>
+        <v>780900</v>
       </c>
       <c r="J33" s="3">
+        <v>2433400</v>
+      </c>
+      <c r="K33" s="3">
         <v>1426500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>763800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3368300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1584100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2056800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>708900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1038300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>762900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-547600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1346000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>825600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1627000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>623200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1915100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>821300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>885300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>939100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>727800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>555500</v>
+        <v>1591600</v>
       </c>
       <c r="E35" s="3">
-        <v>372800</v>
+        <v>569300</v>
       </c>
       <c r="F35" s="3">
-        <v>140500</v>
+        <v>382100</v>
       </c>
       <c r="G35" s="3">
-        <v>1502200</v>
+        <v>144000</v>
       </c>
       <c r="H35" s="3">
-        <v>761900</v>
+        <v>1539600</v>
       </c>
       <c r="I35" s="3">
-        <v>2374300</v>
+        <v>780900</v>
       </c>
       <c r="J35" s="3">
+        <v>2433400</v>
+      </c>
+      <c r="K35" s="3">
         <v>1426500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>763800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3368300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1584100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2056800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>708900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1038300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>762900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-547600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1346000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>825600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1627000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>623200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1915100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>821300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>885300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>939100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>727800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,204 +3588,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>324974100</v>
+        <v>309641800</v>
       </c>
       <c r="E41" s="3">
-        <v>298646000</v>
+        <v>333063100</v>
       </c>
       <c r="F41" s="3">
-        <v>347345600</v>
+        <v>306079700</v>
       </c>
       <c r="G41" s="3">
-        <v>293759100</v>
+        <v>355991500</v>
       </c>
       <c r="H41" s="3">
-        <v>326553000</v>
+        <v>301071200</v>
       </c>
       <c r="I41" s="3">
-        <v>352052100</v>
+        <v>334681300</v>
       </c>
       <c r="J41" s="3">
+        <v>360815100</v>
+      </c>
+      <c r="K41" s="3">
         <v>301050600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>259139700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>330465000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>244721500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>261336700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>217609400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>254792900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>209707300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>225571000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>202919100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>220891500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>163996600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>194104600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>171349700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>197168400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>164605300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>40864500</v>
+        <v>660653500</v>
       </c>
       <c r="E42" s="3">
-        <v>614336900</v>
+        <v>41881700</v>
       </c>
       <c r="F42" s="3">
-        <v>64321100</v>
+        <v>629628500</v>
       </c>
       <c r="G42" s="3">
-        <v>638763900</v>
+        <v>65922100</v>
       </c>
       <c r="H42" s="3">
-        <v>62893500</v>
+        <v>654663600</v>
       </c>
       <c r="I42" s="3">
-        <v>555155600</v>
+        <v>64459000</v>
       </c>
       <c r="J42" s="3">
+        <v>568974100</v>
+      </c>
+      <c r="K42" s="3">
         <v>55417200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>494726400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36272600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>427770700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>35223200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>530635700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>34644200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>467173200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>38143900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>525051700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>37311100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>529056200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>42058800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>579304100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>31521100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>513271000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3797,8 +3889,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3895,8 +3990,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3993,8 +4091,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4091,302 +4192,314 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>246400</v>
+        <v>428600</v>
       </c>
       <c r="E47" s="3">
-        <v>245300</v>
+        <v>252500</v>
       </c>
       <c r="F47" s="3">
-        <v>224800</v>
+        <v>251400</v>
       </c>
       <c r="G47" s="3">
-        <v>225900</v>
+        <v>230400</v>
       </c>
       <c r="H47" s="3">
-        <v>168600</v>
+        <v>231500</v>
       </c>
       <c r="I47" s="3">
-        <v>157800</v>
+        <v>172800</v>
       </c>
       <c r="J47" s="3">
+        <v>161700</v>
+      </c>
+      <c r="K47" s="3">
         <v>124300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>120800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>124800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>103000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>102300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>101600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>109000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>99700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>103800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>115600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>129800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>130700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>317300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>285900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>311000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>294500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>737700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>719200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>768600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>785400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>897600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>817900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>65843800</v>
+        <v>67957900</v>
       </c>
       <c r="E48" s="3">
-        <v>65613600</v>
+        <v>67482700</v>
       </c>
       <c r="F48" s="3">
-        <v>63767800</v>
+        <v>67246800</v>
       </c>
       <c r="G48" s="3">
-        <v>62178100</v>
+        <v>65355000</v>
       </c>
       <c r="H48" s="3">
-        <v>37237700</v>
+        <v>63725800</v>
       </c>
       <c r="I48" s="3">
-        <v>36698400</v>
+        <v>38164600</v>
       </c>
       <c r="J48" s="3">
+        <v>37611900</v>
+      </c>
+      <c r="K48" s="3">
         <v>35715000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35488400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34870800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34656500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33577700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32571600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32128300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30009800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30711500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>32522200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34099900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>33024900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>36724000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>31480500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>34927800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>31643800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5345100</v>
+        <v>5615500</v>
       </c>
       <c r="E49" s="3">
-        <v>5348400</v>
+        <v>5478200</v>
       </c>
       <c r="F49" s="3">
-        <v>5670400</v>
+        <v>5481500</v>
       </c>
       <c r="G49" s="3">
-        <v>5968700</v>
+        <v>5811600</v>
       </c>
       <c r="H49" s="3">
-        <v>4089400</v>
+        <v>6117300</v>
       </c>
       <c r="I49" s="3">
-        <v>4086100</v>
+        <v>4191200</v>
       </c>
       <c r="J49" s="3">
+        <v>4187800</v>
+      </c>
+      <c r="K49" s="3">
         <v>4100200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4128300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4056800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4055600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="O49" s="3">
-        <v>4042600</v>
       </c>
       <c r="P49" s="3">
         <v>4042600</v>
       </c>
       <c r="Q49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="R49" s="3">
         <v>4033500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4199300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4412700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5337300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8160200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5747700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8087800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5457100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5502900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,106 +4697,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>35799300</v>
+        <v>35894000</v>
       </c>
       <c r="E52" s="3">
-        <v>5894100</v>
+        <v>36690400</v>
       </c>
       <c r="F52" s="3">
-        <v>6368600</v>
+        <v>6040900</v>
       </c>
       <c r="G52" s="3">
-        <v>7911800</v>
+        <v>6527100</v>
       </c>
       <c r="H52" s="3">
-        <v>5906000</v>
+        <v>8108700</v>
       </c>
       <c r="I52" s="3">
-        <v>9974900</v>
+        <v>6053000</v>
       </c>
       <c r="J52" s="3">
+        <v>10223100</v>
+      </c>
+      <c r="K52" s="3">
         <v>4869600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4209900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5059400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4181400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5058200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4621300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5898400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4095300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8964300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8922600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10436300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10796200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12949400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16134300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20145200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>22854800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1718919300</v>
+        <v>1763458700</v>
       </c>
       <c r="E54" s="3">
-        <v>1679456400</v>
+        <v>1761705400</v>
       </c>
       <c r="F54" s="3">
-        <v>1728522400</v>
+        <v>1721260200</v>
       </c>
       <c r="G54" s="3">
-        <v>1705809300</v>
+        <v>1771547500</v>
       </c>
       <c r="H54" s="3">
-        <v>1679001500</v>
+        <v>1748269100</v>
       </c>
       <c r="I54" s="3">
-        <v>1604731400</v>
+        <v>1720793900</v>
       </c>
       <c r="J54" s="3">
+        <v>1644675200</v>
+      </c>
+      <c r="K54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,31 +5076,32 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3">
-        <v>33020800</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
-        <v>27436800</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
-        <v>24033700</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>33497100</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3">
+        <v>33842700</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
+        <v>28119700</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
+        <v>24631900</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
@@ -4979,74 +5109,77 @@
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>23345000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>21322900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>19225900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3">
         <v>22898200</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3">
         <v>25886100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3">
         <v>30259400</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="3">
         <v>26338500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5065,11 +5198,11 @@
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I58" s="3">
-        <v>74262500</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3">
+        <v>76110900</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -5077,14 +5210,14 @@
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3">
         <v>121369300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5143,31 +5276,34 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
-        <v>2773100</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2388300</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2820600</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>2670400</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2842100</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2447800</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2890800</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -5175,74 +5311,77 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>2985600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>3007900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>2016700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>1815300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>2759800</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>2592800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
         <v>2834200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5339,204 +5478,213 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>197135900</v>
+        <v>55712300</v>
       </c>
       <c r="E61" s="3">
-        <v>51951400</v>
+        <v>202042900</v>
       </c>
       <c r="F61" s="3">
-        <v>182458900</v>
+        <v>53244500</v>
       </c>
       <c r="G61" s="3">
-        <v>45677900</v>
+        <v>187000500</v>
       </c>
       <c r="H61" s="3">
-        <v>166733600</v>
+        <v>46814900</v>
       </c>
       <c r="I61" s="3">
-        <v>43968300</v>
+        <v>170883900</v>
       </c>
       <c r="J61" s="3">
+        <v>45062700</v>
+      </c>
+      <c r="K61" s="3">
         <v>154313200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>41412000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>164361200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>56119500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>160479600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>53062900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>173731000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>54638600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>166334900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>59718600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>187453200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>61859900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>177461900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>43963200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>168898700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>54097600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>26651100</v>
+        <v>28539500</v>
       </c>
       <c r="E62" s="3">
-        <v>9013000</v>
+        <v>27314500</v>
       </c>
       <c r="F62" s="3">
-        <v>9014100</v>
+        <v>9237400</v>
       </c>
       <c r="G62" s="3">
-        <v>9883000</v>
+        <v>9238500</v>
       </c>
       <c r="H62" s="3">
-        <v>6918600</v>
+        <v>10129000</v>
       </c>
       <c r="I62" s="3">
-        <v>11912600</v>
+        <v>7090900</v>
       </c>
       <c r="J62" s="3">
+        <v>12209100</v>
+      </c>
+      <c r="K62" s="3">
         <v>7178000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7097700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7302100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6968600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6783400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5772400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6505600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5943500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6783700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7107300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6967700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8322500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12323400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15154400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>17011200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>19181900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1646142800</v>
+        <v>1689438900</v>
       </c>
       <c r="E66" s="3">
-        <v>1608157200</v>
+        <v>1687117400</v>
       </c>
       <c r="F66" s="3">
-        <v>1654951600</v>
+        <v>1648186300</v>
       </c>
       <c r="G66" s="3">
-        <v>1632314100</v>
+        <v>1696145400</v>
       </c>
       <c r="H66" s="3">
-        <v>1604706600</v>
+        <v>1672944500</v>
       </c>
       <c r="I66" s="3">
-        <v>1532357000</v>
+        <v>1644649800</v>
       </c>
       <c r="J66" s="3">
+        <v>1570499300</v>
+      </c>
+      <c r="K66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,8 +6323,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>38771200</v>
+        <v>39873600</v>
       </c>
       <c r="E72" s="3">
-        <v>38239500</v>
+        <v>39736300</v>
       </c>
       <c r="F72" s="3">
-        <v>39398000</v>
+        <v>39191300</v>
       </c>
       <c r="G72" s="3">
-        <v>39178600</v>
+        <v>40378700</v>
       </c>
       <c r="H72" s="3">
-        <v>40105900</v>
+        <v>40153800</v>
       </c>
       <c r="I72" s="3">
-        <v>39233700</v>
+        <v>41104100</v>
       </c>
       <c r="J72" s="3">
+        <v>78399300</v>
+      </c>
+      <c r="K72" s="3">
         <v>38343200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>37034600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40266500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>39322500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>37390000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35140400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>34342700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31761200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>32832900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>33673100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>36431500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38298100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39706800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37388300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39071500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38096500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>72776500</v>
+        <v>74019800</v>
       </c>
       <c r="E76" s="3">
-        <v>71299200</v>
+        <v>74588000</v>
       </c>
       <c r="F76" s="3">
-        <v>73570800</v>
+        <v>73073900</v>
       </c>
       <c r="G76" s="3">
-        <v>73495200</v>
+        <v>75402100</v>
       </c>
       <c r="H76" s="3">
-        <v>74294900</v>
+        <v>75324600</v>
       </c>
       <c r="I76" s="3">
-        <v>72374500</v>
+        <v>76144200</v>
       </c>
       <c r="J76" s="3">
+        <v>74176000</v>
+      </c>
+      <c r="K76" s="3">
         <v>71662300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>70271700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71449400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>70539100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>68531800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>66797900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>66569400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>61549600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>62889500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>66173500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>70660200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>74162100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>78050200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>73515600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>73961000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>72187700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>555500</v>
+        <v>1591600</v>
       </c>
       <c r="E81" s="3">
-        <v>372800</v>
+        <v>569300</v>
       </c>
       <c r="F81" s="3">
-        <v>140500</v>
+        <v>382100</v>
       </c>
       <c r="G81" s="3">
-        <v>1502200</v>
+        <v>144000</v>
       </c>
       <c r="H81" s="3">
-        <v>761900</v>
+        <v>1539600</v>
       </c>
       <c r="I81" s="3">
-        <v>2374300</v>
+        <v>780900</v>
       </c>
       <c r="J81" s="3">
+        <v>2433400</v>
+      </c>
+      <c r="K81" s="3">
         <v>1426500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>763800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3368300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1584100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2056800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>708900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1038300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>762900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-547600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1346000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>825600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1627000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>623200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1915100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>821300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>885300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>939100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>727800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,106 +7377,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
-        <v>8332200</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
-        <v>3263700</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
-        <v>5791500</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="D83" s="3">
+        <v>5602200</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
+        <v>8539600</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3">
+        <v>3345000</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
+        <v>5935600</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>5901800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>5249300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
         <v>3003700</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
         <v>3068100</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2769200</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" s="3">
-        <v>40443000</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G89" s="3">
-        <v>23996900</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3">
-        <v>42246700</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="D89" s="3">
+        <v>14437600</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3">
+        <v>41449700</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
+        <v>24594300</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
+        <v>43298300</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>22772600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>80580900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>8778900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3">
         <v>3392700</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>21205800</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,106 +8121,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6196000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6744000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5123000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3099000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6480000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3026000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-13047300</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4232000</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-9727400</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="D94" s="3">
+        <v>-9400200</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-13372100</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-4337400</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-9969500</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,8 +8562,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8393,11 +8626,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8405,11 +8638,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -8417,19 +8650,22 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,186 +8964,192 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-4216900</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-2482400</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-231300</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="D100" s="3">
+        <v>-2900800</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-4321900</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-2544200</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>2160400</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>178600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
         <v>2184600</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-900200</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-2507200</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-2625000</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3">
-        <v>2544000</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="D101" s="3">
+        <v>-646800</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-2569600</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-2690400</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3">
+        <v>2607300</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
         <v>2335200</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
         <v>778700</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3">
         <v>845800</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>947500</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -8918,102 +9166,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E102" s="3">
-        <v>20671600</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G102" s="3">
-        <v>14657500</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3">
-        <v>34820200</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="D102" s="3">
+        <v>1489700</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="3">
+        <v>21186200</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="3">
+        <v>15022400</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3">
+        <v>35686900</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3">
         <v>9436000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>73274000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>4652100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3">
         <v>3339800</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>14449100</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,229 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>31552200</v>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="3">
-        <v>29658200</v>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="3">
-        <v>29141000</v>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
         <v>19131600</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
         <v>14651300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
         <v>11756000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>10311300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>9862300</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
         <v>11817800</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W8" s="3">
         <v>13838500</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="3">
         <v>13949800</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="3">
         <v>13909700</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -978,8 +984,11 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1079,8 +1088,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,31 +1334,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1419,109 +1438,115 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>-900500</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="3">
-        <v>-935900</v>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="3">
-        <v>-919300</v>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="3">
         <v>-885000</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
         <v>-837800</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3">
         <v>-921500</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-841100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3">
         <v>-854800</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15" s="3">
         <v>-814900</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" s="3">
         <v>-889600</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-852900</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="3">
         <v>-611600</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AI15" s="3" t="s">
+      <c r="AJ15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>27046500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>443000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>25289800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>350000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>23225300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>201600</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
         <v>12803900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>492800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8687400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>608700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5863900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>211100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5462500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>292000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6073200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>537600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8143600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>925900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8100700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>403000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8077200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>315800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8066200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>292400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>228400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>574500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>736000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>4505700</v>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F18" s="3">
-        <v>4368400</v>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H18" s="3">
-        <v>5915700</v>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>6327700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>5963900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>5892100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>4848800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>3789100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>3674200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>5737800</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>5872600</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3">
         <v>5843500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,233 +1825,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-1273700</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="3">
-        <v>-2040200</v>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>-2564100</v>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2102200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>-703600</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AJ20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>8834200</v>
+      <c r="D21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="3">
-        <v>10867800</v>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="3">
-        <v>6696500</v>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
         <v>10142300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>11090300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>7409700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>5908300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>6270200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
         <v>6188900</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2096,210 +2135,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>3232000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1312500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2328200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1314700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>3351600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1572800</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
         <v>4225500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2236000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>461400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1468000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5188500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2671800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3437400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1301300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2160400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1514300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-835600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-275500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2904500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1749300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3202200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1312200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3419800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>723300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>303500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1025600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>691100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>834000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>363300</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3">
         <v>911600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>398800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>718100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>361300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1094900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>752800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>726800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>299400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>590500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>484700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>667600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-51900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>722600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>476500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>758800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>305000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>637600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>597000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>840000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>406300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>515000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>775300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>456600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>2508700</v>
-      </c>
-      <c r="E26" s="3">
-        <v>1009000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1302500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>623600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>2517600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1209500</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>3313900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1837200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-256800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1106700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4093600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1919000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2710600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1001900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1569900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1029600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-223600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2181900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1272800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2443400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1007200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2782200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>1591600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>569300</v>
-      </c>
-      <c r="F27" s="3">
-        <v>382100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>144000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1539600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>780900</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>2433400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1426500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>763800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3368300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1584100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2056800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>708900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1038300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>762900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-547600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1346000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>825600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1627000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>623200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1915100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>821300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>885300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>939100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>727800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,31 +2759,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2803,8 +2863,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>1273700</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="3">
-        <v>2040200</v>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
-        <v>2564100</v>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>2102200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>5502500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>703600</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1411400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>1628800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>4509800</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>2833300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3">
         <v>2670400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2423800</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AJ32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>1591600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>569300</v>
-      </c>
-      <c r="F33" s="3">
-        <v>382100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>144000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1539600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>780900</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>2433400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1426500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>763800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3368300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1584100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2056800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>708900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1038300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>762900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-547600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1346000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>825600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1627000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>623200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1915100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>821300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>885300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>939100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>727800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>1591600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>569300</v>
-      </c>
-      <c r="F35" s="3">
-        <v>382100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>144000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1539600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>780900</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>2433400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1426500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>763800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3368300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1584100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2056800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>708900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1038300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>762900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-547600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1346000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>825600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1627000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>623200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1915100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>821300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>885300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>939100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>727800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,233 +3674,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>309641800</v>
+        <v>222105700</v>
       </c>
       <c r="E41" s="3">
-        <v>333063100</v>
+        <v>285282300</v>
       </c>
       <c r="F41" s="3">
-        <v>306079700</v>
+        <v>234898000</v>
       </c>
       <c r="G41" s="3">
-        <v>355991500</v>
+        <v>290533900</v>
       </c>
       <c r="H41" s="3">
-        <v>301071200</v>
+        <v>247675700</v>
       </c>
       <c r="I41" s="3">
-        <v>334681300</v>
+        <v>280915900</v>
       </c>
       <c r="J41" s="3">
+        <v>242447800</v>
+      </c>
+      <c r="K41" s="3">
         <v>360815100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>301050600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>259139700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>330465000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>244721500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>261336700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>217609400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>254792900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>209707300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>225571000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>202919100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>220891500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>163996600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>194104600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>171349700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>197168400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>164605300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>660653500</v>
+        <v>598030300</v>
       </c>
       <c r="E42" s="3">
-        <v>41881700</v>
+        <v>490460700</v>
       </c>
       <c r="F42" s="3">
-        <v>629628500</v>
+        <v>582460900</v>
       </c>
       <c r="G42" s="3">
-        <v>65922100</v>
+        <v>468724400</v>
       </c>
       <c r="H42" s="3">
-        <v>654663600</v>
+        <v>550563100</v>
       </c>
       <c r="I42" s="3">
-        <v>64459000</v>
+        <v>482683400</v>
       </c>
       <c r="J42" s="3">
+        <v>568965700</v>
+      </c>
+      <c r="K42" s="3">
         <v>568974100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>55417200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>494726400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36272600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>427770700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>35223200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>530635700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>34644200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>467173200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>38143900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>525051700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>37311100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>529056200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>42058800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>579304100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>31521100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>513271000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>102261900</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>18892100</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>94427700</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>16369000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>97063900</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>16064400</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>4796800</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3892,31 +3984,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3993,31 +4088,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>44546100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>91860100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>30835000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>80653300</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1684000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>81909400</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1140800</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4094,31 +4192,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>966944000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>888550300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>942621600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>858137500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>896986700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>863599300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>817351200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4195,311 +4296,323 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>428600</v>
+        <v>138397300</v>
       </c>
       <c r="E47" s="3">
-        <v>252500</v>
+        <v>259011000</v>
       </c>
       <c r="F47" s="3">
-        <v>251400</v>
+        <v>127583300</v>
       </c>
       <c r="G47" s="3">
-        <v>230400</v>
+        <v>256926100</v>
       </c>
       <c r="H47" s="3">
-        <v>231500</v>
+        <v>124050600</v>
       </c>
       <c r="I47" s="3">
-        <v>172800</v>
+        <v>242974900</v>
       </c>
       <c r="J47" s="3">
+        <v>131510200</v>
+      </c>
+      <c r="K47" s="3">
         <v>161700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>124300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>120800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>124800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>103000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>102300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>101600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>109000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>99700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>103800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>115600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>129800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>130700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>317300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>285900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>311000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>294500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>737700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>719200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>768600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>785400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>897600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>817900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>67957900</v>
+        <v>68001300</v>
       </c>
       <c r="E48" s="3">
-        <v>67482700</v>
+        <v>61329700</v>
       </c>
       <c r="F48" s="3">
-        <v>67246800</v>
+        <v>65732000</v>
       </c>
       <c r="G48" s="3">
-        <v>65355000</v>
+        <v>62352200</v>
       </c>
       <c r="H48" s="3">
-        <v>63725800</v>
+        <v>62453400</v>
       </c>
       <c r="I48" s="3">
-        <v>38164600</v>
+        <v>62811100</v>
       </c>
       <c r="J48" s="3">
+        <v>37437000</v>
+      </c>
+      <c r="K48" s="3">
         <v>37611900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35715000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35488400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34870800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34656500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33577700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32571600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32128300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30009800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30711500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>32522200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>34099900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33024900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>36724000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>31480500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>34927800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>31643800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5615500</v>
+        <v>5611200</v>
       </c>
       <c r="E49" s="3">
-        <v>5478200</v>
+        <v>9068900</v>
       </c>
       <c r="F49" s="3">
-        <v>5481500</v>
+        <v>5336100</v>
       </c>
       <c r="G49" s="3">
-        <v>5811600</v>
+        <v>9407500</v>
       </c>
       <c r="H49" s="3">
-        <v>6117300</v>
+        <v>5553600</v>
       </c>
       <c r="I49" s="3">
-        <v>4191200</v>
+        <v>6029500</v>
       </c>
       <c r="J49" s="3">
+        <v>4111300</v>
+      </c>
+      <c r="K49" s="3">
         <v>4187800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4100200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4128300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4056800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4055600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>4042600</v>
       </c>
       <c r="Q49" s="3">
         <v>4042600</v>
       </c>
       <c r="R49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="S49" s="3">
         <v>4033500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4199300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4412700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5337300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8160200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5747700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8087800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5457100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5502900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,109 +4816,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>35894000</v>
+        <v>84721200</v>
       </c>
       <c r="E52" s="3">
-        <v>36690400</v>
+        <v>9631400</v>
       </c>
       <c r="F52" s="3">
-        <v>6040900</v>
+        <v>79254500</v>
       </c>
       <c r="G52" s="3">
-        <v>6527100</v>
+        <v>5848300</v>
       </c>
       <c r="H52" s="3">
-        <v>8108700</v>
+        <v>87563500</v>
       </c>
       <c r="I52" s="3">
-        <v>6053000</v>
+        <v>8104800</v>
       </c>
       <c r="J52" s="3">
+        <v>74657800</v>
+      </c>
+      <c r="K52" s="3">
         <v>10223100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4869600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4209900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5059400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4181400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5058200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4621300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5898400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4095300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8964300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8922600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10436300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10796200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12949400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16134300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20145200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>22854800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1763458700</v>
+        <v>1761752200</v>
       </c>
       <c r="E54" s="3">
-        <v>1761705400</v>
+        <v>1705929500</v>
       </c>
       <c r="F54" s="3">
-        <v>1721260200</v>
+        <v>1716000600</v>
       </c>
       <c r="G54" s="3">
-        <v>1771547500</v>
+        <v>1717746200</v>
       </c>
       <c r="H54" s="3">
-        <v>1748269100</v>
+        <v>1692894800</v>
       </c>
       <c r="I54" s="3">
-        <v>1720793900</v>
+        <v>1723176900</v>
       </c>
       <c r="J54" s="3">
+        <v>1687987800</v>
+      </c>
+      <c r="K54" s="3">
         <v>1644675200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,150 +5206,154 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>33497100</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>4</v>
+        <v>586772300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>670938600</v>
       </c>
       <c r="F57" s="3">
-        <v>33842700</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
+        <v>572820200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>712377600</v>
       </c>
       <c r="H57" s="3">
-        <v>28119700</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
+        <v>575697500</v>
+      </c>
+      <c r="I57" s="3">
+        <v>713595000</v>
       </c>
       <c r="J57" s="3">
+        <v>582603200</v>
+      </c>
+      <c r="K57" s="3">
         <v>24631900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>23345000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3">
         <v>21322900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="3">
         <v>19225900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3">
         <v>22898200</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W57" s="3">
         <v>25886100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y57" s="3">
         <v>30259400</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA57" s="3">
         <v>26338500</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AI57" s="3" t="s">
+      <c r="AJ57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>21950700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>141919000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>23454500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>209366600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>464061200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>385420300</v>
       </c>
       <c r="J58" s="3">
+        <v>48867900</v>
+      </c>
+      <c r="K58" s="3">
         <v>76110900</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3">
         <v>121369300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -5279,132 +5412,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2670400</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
+        <v>36045100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>238126000</v>
       </c>
       <c r="F59" s="3">
-        <v>2842100</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
+        <v>22035800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>228724400</v>
       </c>
       <c r="H59" s="3">
-        <v>2447800</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+        <v>4253800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3342800</v>
       </c>
       <c r="J59" s="3">
+        <v>2184900</v>
+      </c>
+      <c r="K59" s="3">
         <v>2890800</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>2985600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>3007900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S59" s="3">
         <v>2016700</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3">
         <v>1815300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
         <v>2759800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3">
         <v>2592800</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3">
         <v>2834200</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AI59" s="3" t="s">
+      <c r="AJ59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>644768000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1058070300</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>618310500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1156958100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1044012500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1108622300</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>633656000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5481,210 +5620,219 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>55712300</v>
+        <v>317089000</v>
       </c>
       <c r="E61" s="3">
-        <v>202042900</v>
+        <v>191327500</v>
       </c>
       <c r="F61" s="3">
-        <v>53244500</v>
+        <v>318936200</v>
       </c>
       <c r="G61" s="3">
-        <v>187000500</v>
+        <v>125073500</v>
       </c>
       <c r="H61" s="3">
-        <v>46814900</v>
+        <v>304189200</v>
       </c>
       <c r="I61" s="3">
-        <v>170883900</v>
+        <v>182185600</v>
       </c>
       <c r="J61" s="3">
+        <v>308690800</v>
+      </c>
+      <c r="K61" s="3">
         <v>45062700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>154313200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>41412000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>164361200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>56119500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>160479600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>53062900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>173731000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>54638600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>166334900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>59718600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>187453200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>61859900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>177461900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>43963200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>168898700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>54097600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>28539500</v>
+        <v>713747500</v>
       </c>
       <c r="E62" s="3">
-        <v>27314500</v>
+        <v>369303500</v>
       </c>
       <c r="F62" s="3">
-        <v>9237400</v>
+        <v>694836600</v>
       </c>
       <c r="G62" s="3">
-        <v>9238500</v>
+        <v>345750000</v>
       </c>
       <c r="H62" s="3">
-        <v>10129000</v>
+        <v>261863900</v>
       </c>
       <c r="I62" s="3">
-        <v>7090900</v>
+        <v>341551300</v>
       </c>
       <c r="J62" s="3">
+        <v>663752700</v>
+      </c>
+      <c r="K62" s="3">
         <v>12209100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7178000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7097700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7302100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6968600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6783400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5772400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6505600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5943500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6783700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7107300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6967700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8322500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12323400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15154400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17011200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>19181900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1689438900</v>
+        <v>1675604500</v>
       </c>
       <c r="E66" s="3">
-        <v>1687117400</v>
+        <v>1624056600</v>
       </c>
       <c r="F66" s="3">
-        <v>1648186300</v>
+        <v>1632083300</v>
       </c>
       <c r="G66" s="3">
-        <v>1696145400</v>
+        <v>1633467400</v>
       </c>
       <c r="H66" s="3">
-        <v>1672944500</v>
+        <v>1610065600</v>
       </c>
       <c r="I66" s="3">
-        <v>1644649800</v>
+        <v>1638041500</v>
       </c>
       <c r="J66" s="3">
+        <v>1606099500</v>
+      </c>
+      <c r="K66" s="3">
         <v>1570499300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6490,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>39873600</v>
+        <v>41528000</v>
       </c>
       <c r="E72" s="3">
-        <v>39736300</v>
+        <v>38572800</v>
       </c>
       <c r="F72" s="3">
-        <v>39191300</v>
+        <v>38705400</v>
       </c>
       <c r="G72" s="3">
-        <v>40378700</v>
+        <v>39111300</v>
       </c>
       <c r="H72" s="3">
-        <v>40153800</v>
+        <v>38585900</v>
       </c>
       <c r="I72" s="3">
-        <v>41104100</v>
+        <v>39577500</v>
       </c>
       <c r="J72" s="3">
+        <v>40320500</v>
+      </c>
+      <c r="K72" s="3">
         <v>78399300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>38343200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>37034600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40266500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>39322500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>37390000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>35140400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>34342700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>31761200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>32832900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33673100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36431500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38298100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>39706800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>37388300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>39071500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>38096500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>74019800</v>
+        <v>75224200</v>
       </c>
       <c r="E76" s="3">
-        <v>74588000</v>
+        <v>71605100</v>
       </c>
       <c r="F76" s="3">
-        <v>73073900</v>
+        <v>72652900</v>
       </c>
       <c r="G76" s="3">
-        <v>75402100</v>
+        <v>72924700</v>
       </c>
       <c r="H76" s="3">
-        <v>75324600</v>
+        <v>72054400</v>
       </c>
       <c r="I76" s="3">
-        <v>76144200</v>
+        <v>74243400</v>
       </c>
       <c r="J76" s="3">
+        <v>74692500</v>
+      </c>
+      <c r="K76" s="3">
         <v>74176000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71662300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>70271700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71449400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>70539100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>68531800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>66797900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66569400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>61549600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>62889500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>66173500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>70660200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>74162100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>78050200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>73515600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>73961000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>72187700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>1591600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>569300</v>
-      </c>
-      <c r="F81" s="3">
-        <v>382100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>144000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1539600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>780900</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>2433400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1426500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>763800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3368300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1584100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2056800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>708900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1038300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>762900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-547600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1346000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>825600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1627000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>623200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1915100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>821300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>885300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>939100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>727800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>5602200</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="3">
-        <v>8539600</v>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="3">
-        <v>3345000</v>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>5935600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3">
         <v>5901800</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3">
         <v>5249300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W83" s="3">
         <v>3003700</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
         <v>3068100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="3">
         <v>2769200</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AJ83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>14437600</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F89" s="3">
-        <v>41449700</v>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H89" s="3">
-        <v>24594300</v>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>43298300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
         <v>22772600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S89" s="3">
         <v>80580900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W89" s="3">
         <v>8778900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3">
         <v>3392700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA89" s="3">
         <v>21205800</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AJ89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-6196000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-6744000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-5123000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3099000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-6480000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-3026000</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-9400200</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>-13372100</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H94" s="3">
-        <v>-4337400</v>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9969500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AJ94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,31 +8795,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8629,11 +8862,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8641,11 +8874,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8653,19 +8886,22 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,192 +9209,198 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-2900800</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F100" s="3">
-        <v>-4321900</v>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H100" s="3">
-        <v>-2544200</v>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>-237000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
         <v>2160400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W100" s="3">
         <v>178600</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3">
         <v>2184600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-900200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-646800</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="3">
-        <v>-2569600</v>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H101" s="3">
-        <v>-2690400</v>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3">
         <v>2607300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3">
         <v>2335200</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W101" s="3">
         <v>778700</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y101" s="3">
         <v>845800</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA101" s="3">
         <v>947500</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
+      <c r="AD101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -9169,105 +9417,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>1489700</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F102" s="3">
-        <v>21186200</v>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H102" s="3">
-        <v>15022400</v>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K102" s="3">
         <v>35686900</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3">
         <v>9436000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S102" s="3">
         <v>73274000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3">
         <v>4652100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3">
         <v>3339800</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3">
         <v>14449100</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,131 +656,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -805,86 +808,89 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
         <v>19131600</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>14651300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>11756000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>10311300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>9862300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>11817800</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>13838500</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>13949800</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>13909700</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AK8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -987,8 +993,11 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1091,8 +1100,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,8 +1353,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1363,8 +1382,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1441,8 +1460,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,86 +1489,89 @@
       <c r="J15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="3">
         <v>-885000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
         <v>-837800</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>-921500</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>-841100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3">
         <v>-854800</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>-814900</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>-889600</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-852900</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-611600</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AJ15" s="3" t="s">
+      <c r="AK15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,8 +1605,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1606,86 +1632,89 @@
       <c r="J17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="3">
         <v>12803900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>492800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8687400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>608700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5863900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>211100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5462500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>292000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6073200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>537600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8143600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>925900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8100700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>403000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8077200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>315800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8066200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>292400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>228400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>574500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>736000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1710,86 +1739,89 @@
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>6327700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>5963900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>5892100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>4848800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>3789100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>3674200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>5737800</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>5872600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>5843500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AK18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,8 +1858,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1852,86 +1885,89 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2102200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-703600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AK20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1956,86 +1992,89 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3">
         <v>10142300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>11090300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>7409700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>5908300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>6270200</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>6188900</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2060,8 +2099,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2138,8 +2177,11 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2164,86 +2206,89 @@
       <c r="J23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3">
         <v>4225500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2236000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>461400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1468000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5188500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2671800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3437400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1301300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2160400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1514300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-835600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-275500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2904500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1749300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3202200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1312200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3419800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2268,86 +2313,89 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
         <v>911600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>398800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>718100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>361300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1094900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>752800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>726800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>299400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>590500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>484700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>667600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-51900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>722600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>476500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>758800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>305000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>637600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>597000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>840000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>406300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>515000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>775300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>456600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,8 +2498,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2476,86 +2527,89 @@
       <c r="J26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3">
         <v>3313900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1837200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-256800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1106700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4093600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1919000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2710600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1001900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1569900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1029600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-223600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2181900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1272800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2443400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1007200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2782200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2580,86 +2634,89 @@
       <c r="J27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3">
         <v>2433400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1426500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>763800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3368300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1584100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2056800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>708900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1038300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>762900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-547600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1346000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>825600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1627000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>623200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1915100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>821300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>885300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>939100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>727800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2788,8 +2848,8 @@
       <c r="J29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2866,8 +2926,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,8 +3140,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3100,86 +3169,89 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>2102200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>5502500</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>703600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>1411400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>1628800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>4509800</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>2833300</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2670400</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2423800</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AK32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3204,86 +3276,89 @@
       <c r="J33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3">
         <v>2433400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1426500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>763800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3368300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1584100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2056800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>708900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1038300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>762900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-547600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1346000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>825600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1627000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>623200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1915100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>821300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>885300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>939100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>727800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,8 +3461,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3412,195 +3490,201 @@
       <c r="J35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" s="3">
         <v>2433400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1426500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>763800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3368300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1584100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2056800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>708900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1038300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>762900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-547600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1346000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>825600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1627000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>623200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1915100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>821300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>885300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>939100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>727800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,243 +3760,250 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>208800100</v>
+      </c>
+      <c r="E41" s="3">
         <v>222105700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>285282300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>234898000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>290533900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>247675700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>280915900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>242447800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>360815100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>301050600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>259139700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>330465000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>244721500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>261336700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>217609400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>254792900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>209707300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>225571000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>202919100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>220891500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>163996600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>194104600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>171349700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>197168400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>164605300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>553876200</v>
+      </c>
+      <c r="E42" s="3">
         <v>598030300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>490460700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>582460900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>468724400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>550563100</v>
       </c>
-      <c r="I42" s="3">
-        <v>482683400</v>
-      </c>
       <c r="J42" s="3">
+        <v>498040400</v>
+      </c>
+      <c r="K42" s="3">
         <v>568965700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>568974100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>55417200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>494726400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>36272600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>427770700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>35223200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>530635700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>34644200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>467173200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>38143900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>525051700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>37311100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>529056200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>42058800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>579304100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>31521100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>513271000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>91870800</v>
+      </c>
+      <c r="E43" s="3">
         <v>102261900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18892100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>94427700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16369000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>97063900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16064400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4796800</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3987,8 +4079,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4013,8 +4108,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4091,35 +4186,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27358900</v>
+      </c>
+      <c r="E45" s="3">
         <v>44546100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>91860100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30835000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>80653300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1684000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>81909400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1140800</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4195,35 +4293,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>881906000</v>
+      </c>
+      <c r="E46" s="3">
         <v>966944000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>888550300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>942621600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>858137500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>896986700</v>
       </c>
-      <c r="I46" s="3">
-        <v>863599300</v>
-      </c>
       <c r="J46" s="3">
+        <v>878956300</v>
+      </c>
+      <c r="K46" s="3">
         <v>817351200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4299,320 +4400,332 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>133633900</v>
+      </c>
+      <c r="E47" s="3">
         <v>138397300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>259011000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>127583300</v>
       </c>
-      <c r="G47" s="3">
-        <v>256926100</v>
-      </c>
       <c r="H47" s="3">
+        <v>256665200</v>
+      </c>
+      <c r="I47" s="3">
         <v>124050600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>242974900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>131510200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>161700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>124300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>120800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>124800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>103000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>102300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>101600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>109000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>99700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>103800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>115600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>129800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>130700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>317300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>285900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>311000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>294500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>737700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>719200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>768600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>785400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>897600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>817900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>63577000</v>
+      </c>
+      <c r="E48" s="3">
         <v>68001300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>61329700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>65732000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>62352200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>62453400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>62811100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37437000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37611900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35715000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35488400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34870800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34656500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>33577700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32571600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32128300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30009800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30711500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>32522200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>34099900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33024900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>36724000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>31480500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>34927800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>31643800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5265600</v>
+      </c>
+      <c r="E49" s="3">
         <v>5611200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9068900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5336100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9407500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5553600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6029500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4111300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4187800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4100200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4128300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4056800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4055600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>4042600</v>
       </c>
       <c r="R49" s="3">
         <v>4042600</v>
       </c>
       <c r="S49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="T49" s="3">
         <v>4033500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4199300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4412700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5337300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8160200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5747700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8087800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5457100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5502900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,112 +4935,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74042900</v>
+      </c>
+      <c r="E52" s="3">
         <v>84721200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9631400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>79254500</v>
       </c>
-      <c r="G52" s="3">
-        <v>5848300</v>
-      </c>
       <c r="H52" s="3">
+        <v>6109200</v>
+      </c>
+      <c r="I52" s="3">
         <v>87563500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8104800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>74657800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10223100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4869600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4209900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5059400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4181400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5058200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4621300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5898400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4095300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8964300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8922600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10436300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10796200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12949400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16134300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20145200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>22854800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1629097200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1761752200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1705929500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1716000600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1717746200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1692894800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1723176900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1687987800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1644675200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,156 +5336,160 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>550445200</v>
+      </c>
+      <c r="E57" s="3">
         <v>586772300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>670938600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>572820200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>712377600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>575697500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>713595000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>582603200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24631900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>23345000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>21322900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3">
         <v>19225900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3">
         <v>22898200</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3">
         <v>25886100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="3">
         <v>30259400</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="3">
         <v>26338500</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AJ57" s="3" t="s">
+      <c r="AK57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22607900</v>
+      </c>
+      <c r="E58" s="3">
         <v>21950700</v>
       </c>
-      <c r="E58" s="3">
-        <v>141919000</v>
-      </c>
       <c r="F58" s="3">
+        <v>301954400</v>
+      </c>
+      <c r="G58" s="3">
         <v>23454500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>209366600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>464061200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>385420300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48867900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>76110900</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P58" s="3">
         <v>121369300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5415,139 +5548,145 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19997900</v>
+      </c>
+      <c r="E59" s="3">
         <v>36045100</v>
       </c>
-      <c r="E59" s="3">
-        <v>238126000</v>
-      </c>
       <c r="F59" s="3">
+        <v>78090600</v>
+      </c>
+      <c r="G59" s="3">
         <v>22035800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>228724400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4253800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3342800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2184900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2890800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>2985600</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>3007900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>2016700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>1815300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>2759800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
         <v>2592800</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>2834200</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AJ59" s="3" t="s">
+      <c r="AK59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>593051000</v>
+      </c>
+      <c r="E60" s="3">
         <v>644768000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1058070300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>618310500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1156958100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1044012500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1108622300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>633656000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5623,216 +5762,225 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>288801100</v>
+      </c>
+      <c r="E61" s="3">
         <v>317089000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>191327500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>318936200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>125073500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>304189200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>182185600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>308690800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>45062700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>154313200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>41412000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>164361200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>56119500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>160479600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>53062900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>173731000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>54638600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>166334900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>59718600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>187453200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>61859900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>177461900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>43963200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>168898700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>54097600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>664847300</v>
+      </c>
+      <c r="E62" s="3">
         <v>713747500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>369303500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>694836600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>345750000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>261863900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>341551300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>663752700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12209100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7178000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7097700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7302100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6968600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6783400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5772400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6505600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5943500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6783700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7107300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6967700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8322500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12323400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15154400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>17011200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>19181900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1546699500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1675604500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1624056600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1632083300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1633467400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1610065600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1638041500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1606099500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1570499300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,8 +6657,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>39406800</v>
+      </c>
+      <c r="E72" s="3">
         <v>41528000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>38572800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>38705400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>39111300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>38585900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39577500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>40320500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>78399300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38343200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>37034600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40266500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>39322500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>37390000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>35140400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>34342700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31761200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>32832900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33673100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36431500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38298100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39706800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37388300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39071500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>38096500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AK72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>72736300</v>
+      </c>
+      <c r="E76" s="3">
         <v>75224200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>71605100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72652900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72924700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72054400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74243400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74692500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74176000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71662300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>70271700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71449400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>70539100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>68531800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>66797900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>66569400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>61549600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>62889500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>66173500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>70660200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>74162100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>78050200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>73515600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>73961000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>72187700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,117 +7513,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7460,86 +7654,89 @@
       <c r="J81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3">
         <v>2433400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1426500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>763800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3368300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1584100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2056800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>708900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1038300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>762900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-547600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1346000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>825600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1627000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>623200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1915100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>821300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>885300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>939100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>727800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,8 +7773,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7602,86 +7800,89 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>5935600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
         <v>5901800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
         <v>5249300</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
         <v>3003700</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
         <v>3068100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2769200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AK83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,8 +8413,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8226,86 +8442,89 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
         <v>43298300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>22772600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>80580900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3">
         <v>8778900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>3392700</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
         <v>21205800</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AK89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,8 +8561,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8368,86 +8588,89 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AK91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,8 +8880,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8680,86 +8909,89 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3">
         <v>-9969500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AJ94" s="3" t="s">
+      <c r="AK94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,8 +9028,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8822,8 +9055,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8865,11 +9098,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8877,11 +9110,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -8889,19 +9122,22 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,8 +9454,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9238,86 +9483,89 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3">
         <v>-237000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
         <v>2160400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
         <v>178600</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>2184600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-900200</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AJ100" s="3" t="s">
+      <c r="AK100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9342,68 +9590,68 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>2607300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3">
         <v>2335200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3">
         <v>778700</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>845800</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB101" s="3">
         <v>947500</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>0</v>
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
@@ -9420,8 +9668,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9446,82 +9697,85 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3">
         <v>35686900</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3">
         <v>9436000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>73274000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3">
         <v>4652100</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>3339800</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
         <v>14449100</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AJ102" s="3" t="s">
+      <c r="AK102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,134 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -811,86 +814,89 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
         <v>19131600</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
         <v>14651300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>11756000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>10311300</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
         <v>9862300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W8" s="3">
         <v>11817800</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="3">
         <v>13838500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="3">
         <v>13949800</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3">
         <v>13909700</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="3">
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AK8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -996,8 +1002,11 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,8 +1372,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1385,8 +1404,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1463,8 +1482,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,86 +1514,89 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
         <v>-885000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3">
         <v>-837800</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-921500</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3">
         <v>-841100</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15" s="3">
         <v>-854800</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" s="3">
         <v>-814900</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-889600</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="3">
         <v>-852900</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-611600</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AK15" s="3" t="s">
+      <c r="AL15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,8 +1631,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1635,86 +1661,89 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
         <v>12803900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>492800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8687400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>608700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5863900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>211100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5462500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>292000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6073200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>537600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8143600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>925900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8100700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>403000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8077200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>315800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8066200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>292400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>228400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>574500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>736000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1742,86 +1771,89 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>6327700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>5963900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>5892100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>4848800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>3789100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>3674200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>5737800</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3">
         <v>5872600</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3">
         <v>5843500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AK18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,8 +1891,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1888,86 +1921,89 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2102200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-703600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AL20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1995,86 +2031,89 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>10142300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>11090300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>7409700</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>5908300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
         <v>6270200</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3">
         <v>6188900</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2102,8 +2141,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2180,8 +2219,11 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2209,86 +2251,89 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
         <v>4225500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2236000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>461400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1468000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5188500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2671800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3437400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1301300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2160400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1514300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-835600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-275500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2904500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1749300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3202200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1312200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3419800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2316,86 +2361,89 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>911600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>398800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>718100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>361300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1094900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>752800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>726800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>299400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>590500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>484700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>667600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-51900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>722600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>476500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>758800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>305000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>637600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>597000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>840000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>406300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>515000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>775300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>456600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,8 +2549,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2530,86 +2581,89 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
         <v>3313900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1837200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-256800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1106700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4093600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1919000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2710600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1001900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1569900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1029600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-223600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2181900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1272800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2443400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1007200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2782200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2637,86 +2691,89 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
         <v>2433400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1426500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>763800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3368300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1584100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2056800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>708900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1038300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>762900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-547600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1346000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>825600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1627000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>623200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1915100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>821300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>885300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>939100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>727800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2851,8 +2911,8 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2929,8 +2989,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,8 +3209,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3172,86 +3241,89 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>2102200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>5502500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>703600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>1411400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>1628800</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>4509800</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3">
         <v>2833300</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2670400</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="3">
         <v>2423800</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AL32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3279,86 +3351,89 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
         <v>2433400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1426500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>763800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3368300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1584100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2056800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>708900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1038300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>762900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-547600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1346000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>825600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1627000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>623200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1915100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>821300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>885300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>939100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>727800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,8 +3539,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3493,198 +3571,204 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
         <v>2433400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1426500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>763800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3368300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1584100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2056800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>708900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1038300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>762900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-547600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1346000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>825600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1627000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>623200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1915100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>821300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>885300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>939100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>727800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,252 +3846,259 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>208800100</v>
+        <v>183626200</v>
       </c>
       <c r="E41" s="3">
+        <v>254869000</v>
+      </c>
+      <c r="F41" s="3">
         <v>222105700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>285282300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>234898000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>290533900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>247675700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>280915900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>242447800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>360815100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>301050600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>259139700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>330465000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>244721500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>261336700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>217609400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>254792900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>209707300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>225571000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>202919100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>220891500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>163996600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>194104600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>171349700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>197168400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>164605300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>553876200</v>
+        <v>601696900</v>
       </c>
       <c r="E42" s="3">
+        <v>435670400</v>
+      </c>
+      <c r="F42" s="3">
         <v>598030300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>490460700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>582460900</v>
       </c>
-      <c r="H42" s="3">
-        <v>468724400</v>
-      </c>
       <c r="I42" s="3">
+        <v>454422500</v>
+      </c>
+      <c r="J42" s="3">
         <v>550563100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>498040400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>568965700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>568974100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>55417200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>494726400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>36272600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>427770700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>35223200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>530635700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>34644200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>467173200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>38143900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>525051700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>37311100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>529056200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>42058800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>579304100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>31521100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>513271000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>91870800</v>
+        <v>103433900</v>
       </c>
       <c r="E43" s="3">
+        <v>15679700</v>
+      </c>
+      <c r="F43" s="3">
         <v>102261900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18892100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>94427700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16369000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>97063900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16064400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4796800</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4082,8 +4174,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4111,8 +4206,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4189,38 +4284,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>27358900</v>
+        <v>3146300</v>
       </c>
       <c r="E45" s="3">
+        <v>110808600</v>
+      </c>
+      <c r="F45" s="3">
         <v>44546100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>91860100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30835000</v>
       </c>
-      <c r="H45" s="3">
-        <v>80653300</v>
-      </c>
       <c r="I45" s="3">
+        <v>82510200</v>
+      </c>
+      <c r="J45" s="3">
         <v>1684000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>81909400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1140800</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4296,38 +4394,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>881906000</v>
+        <v>1375923000</v>
       </c>
       <c r="E46" s="3">
+        <v>817027600</v>
+      </c>
+      <c r="F46" s="3">
         <v>966944000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>888550300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>942621600</v>
       </c>
-      <c r="H46" s="3">
-        <v>858137500</v>
-      </c>
       <c r="I46" s="3">
+        <v>843835500</v>
+      </c>
+      <c r="J46" s="3">
         <v>896986700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>878956300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>817351200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4403,329 +4504,341 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>133633900</v>
+        <v>152276300</v>
       </c>
       <c r="E47" s="3">
+        <v>257400400</v>
+      </c>
+      <c r="F47" s="3">
         <v>138397300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>259011000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>127583300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>256665200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>124050600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>242974900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>131510200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>161700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>124300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>120800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>124800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>103000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>102300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>101600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>109000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>99700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>103800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>115600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>129800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>130700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>317300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>285900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>311000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>294500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>737700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>719200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>768600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>785400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>897600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>817900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>63577000</v>
+        <v>66201900</v>
       </c>
       <c r="E48" s="3">
+        <v>59330200</v>
+      </c>
+      <c r="F48" s="3">
         <v>68001300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>61329700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>65732000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>62352200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>62453400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>62811100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37437000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37611900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35715000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35488400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34870800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34656500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33577700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32571600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>32128300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30009800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30711500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>32522200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>34099900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33024900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>36724000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>31480500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>34927800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>31643800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5265600</v>
+        <v>5496100</v>
       </c>
       <c r="E49" s="3">
+        <v>8778300</v>
+      </c>
+      <c r="F49" s="3">
         <v>5611200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9068900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5336100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9407500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5553600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6029500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4111300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4187800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4100200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4128300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4056800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4055600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="R49" s="3">
-        <v>4042600</v>
       </c>
       <c r="S49" s="3">
         <v>4042600</v>
       </c>
       <c r="T49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="U49" s="3">
         <v>4033500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4199300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4412700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5337300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8160200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5747700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8087800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5457100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5502900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,115 +5054,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>74042900</v>
+        <v>80158900</v>
       </c>
       <c r="E52" s="3">
+        <v>7712000</v>
+      </c>
+      <c r="F52" s="3">
         <v>84721200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9631400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>79254500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6109200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>87563500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8104800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>74657800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10223100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4869600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4209900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5059400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4181400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5058200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4621300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5898400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4095300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8964300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8922600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10436300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10796200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12949400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16134300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20145200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22854800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1680056200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1629097200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1761752200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1705929500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1716000600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1717746200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1692894800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1723176900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1687987800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1644675200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,162 +5466,166 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>550445200</v>
+        <v>563273900</v>
       </c>
       <c r="E57" s="3">
+        <v>635552300</v>
+      </c>
+      <c r="F57" s="3">
         <v>586772300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>670938600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>572820200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>712377600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>575697500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>713595000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>582603200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24631900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3">
         <v>23345000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="3">
         <v>21322900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3">
         <v>19225900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W57" s="3">
         <v>22898200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y57" s="3">
         <v>25886100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA57" s="3">
         <v>30259400</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC57" s="3">
         <v>26338500</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AK57" s="3" t="s">
+      <c r="AL57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22607900</v>
+        <v>20018400</v>
       </c>
       <c r="E58" s="3">
+        <v>216699500</v>
+      </c>
+      <c r="F58" s="3">
         <v>21950700</v>
       </c>
-      <c r="F58" s="3">
-        <v>301954400</v>
-      </c>
       <c r="G58" s="3">
+        <v>141919000</v>
+      </c>
+      <c r="H58" s="3">
         <v>23454500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>209366600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>464061200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>385420300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>48867900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>76110900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3">
         <v>121369300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5551,145 +5684,151 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19997900</v>
+        <v>5254000</v>
       </c>
       <c r="E59" s="3">
+        <v>231331400</v>
+      </c>
+      <c r="F59" s="3">
         <v>36045100</v>
       </c>
-      <c r="F59" s="3">
-        <v>78090600</v>
-      </c>
       <c r="G59" s="3">
+        <v>238126000</v>
+      </c>
+      <c r="H59" s="3">
         <v>22035800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>228724400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4253800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3342800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2184900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2890800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2985600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S59" s="3">
         <v>3007900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3">
         <v>2016700</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
         <v>1815300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3">
         <v>2759800</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3">
         <v>2592800</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3">
         <v>2834200</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AK59" s="3" t="s">
+      <c r="AL59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>593051000</v>
+        <v>588546300</v>
       </c>
       <c r="E60" s="3">
+        <v>1088663400</v>
+      </c>
+      <c r="F60" s="3">
         <v>644768000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1058070300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>618310500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1156958100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1044012500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1108622300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>633656000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5765,222 +5904,231 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>288801100</v>
+        <v>293265200</v>
       </c>
       <c r="E61" s="3">
+        <v>118668600</v>
+      </c>
+      <c r="F61" s="3">
         <v>317089000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>191327500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>318936200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>125073500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>304189200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>182185600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>308690800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45062700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>154313200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>41412000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>164361200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>56119500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>160479600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>53062900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>173731000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>54638600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>166334900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>59718600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>187453200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>61859900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>177461900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>43963200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>168898700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>54097600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>664847300</v>
+        <v>711705600</v>
       </c>
       <c r="E62" s="3">
+        <v>334438300</v>
+      </c>
+      <c r="F62" s="3">
         <v>713747500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>369303500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>694836600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>345750000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>261863900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>341551300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>663752700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12209100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7178000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7097700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7302100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6968600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6783400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5772400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6505600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5943500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6783700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7107300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6967700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8322500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12323400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15154400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>17011200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>19181900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1593517100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1546699500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1675604500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1624056600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1632083300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1633467400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1610065600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1638041500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1606099500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1570499300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,8 +6824,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>42662100</v>
+      </c>
+      <c r="E72" s="3">
         <v>39406800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>41528000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>38572800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>38705400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>39111300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>38585900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>39577500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40320500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>78399300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38343200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>37034600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40266500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>39322500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>37390000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>35140400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>34342700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>31761200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>32832900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33673100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>36431500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38298100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>39706800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>37388300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39071500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>38096500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AK72" s="3" t="s">
+      <c r="AL72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>76260300</v>
+      </c>
+      <c r="E76" s="3">
         <v>72736300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>75224200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>71605100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72652900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72924700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>72054400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74243400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74692500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>74176000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71662300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>70271700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71449400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>70539100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>68531800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>66797900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>66569400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>61549600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>62889500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>66173500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>70660200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>74162100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>78050200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>73515600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>73961000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>72187700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,120 +7704,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7657,86 +7851,89 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
         <v>2433400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1426500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>763800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3368300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1584100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2056800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>708900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1038300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>762900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-547600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1346000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>825600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1627000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>623200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1915100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>821300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>885300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>939100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>727800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,8 +7971,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7803,86 +8001,89 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>5935600</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5901800</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3">
         <v>5249300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
         <v>3003700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="3">
         <v>3068100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2769200</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AK83" s="3" t="s">
+      <c r="AL83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,8 +8629,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8445,86 +8661,89 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>43298300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
         <v>22772600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3">
         <v>80580900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3">
         <v>8778900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA89" s="3">
         <v>3392700</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC89" s="3">
         <v>21205800</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AL89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,8 +8781,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8591,86 +8811,89 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AK91" s="3" t="s">
+      <c r="AL91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,8 +9109,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8912,86 +9141,89 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-9969500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AK94" s="3" t="s">
+      <c r="AL94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,8 +9261,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9058,8 +9291,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9101,11 +9334,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -9113,11 +9346,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -9125,19 +9358,22 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,8 +9699,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9486,86 +9731,89 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>-237000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3">
         <v>2160400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3">
         <v>178600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2184600</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-900200</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9593,68 +9841,68 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3">
         <v>2607300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3">
         <v>2335200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y101" s="3">
         <v>778700</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA101" s="3">
         <v>845800</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC101" s="3">
         <v>947500</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>0</v>
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG101" s="3">
         <v>0</v>
@@ -9671,8 +9919,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9700,82 +9951,85 @@
       <c r="K102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3">
         <v>35686900</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3">
         <v>9436000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3">
         <v>73274000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3">
         <v>4652100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3">
         <v>3339800</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC102" s="3">
         <v>14449100</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,137 +656,142 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="39" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -817,86 +822,89 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>19131600</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>14651300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>11756000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>10311300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>9862300</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>11817800</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>13838500</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>13949800</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>13909700</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AL8" s="3" t="s">
+      <c r="AM8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1005,8 +1013,11 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1115,8 +1126,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1155,8 +1169,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1265,8 +1280,11 @@
       <c r="AL12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,8 +1393,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1407,8 +1428,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1485,8 +1506,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,86 +1541,89 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
         <v>-885000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>-837800</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>-921500</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3">
         <v>-841100</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>-854800</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>-814900</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-889600</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-852900</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-611600</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AL15" s="3" t="s">
+      <c r="AM15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,8 +1659,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1664,86 +1692,89 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3">
         <v>12803900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>492800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8687400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>608700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5863900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>211100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5462500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>292000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6073200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>537600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8143600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>925900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8100700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>403000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8077200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>315800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8066200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>292400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>228400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>574500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>736000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1774,86 +1805,89 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>6327700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>5963900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>5892100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>4848800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>3789100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>3674200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>5737800</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>5872600</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5843500</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AL18" s="3" t="s">
+      <c r="AM18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,8 +1926,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1924,86 +1959,89 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-2102200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-703600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AL20" s="3" t="s">
+      <c r="AM20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2034,86 +2072,89 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>10142300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>11090300</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>7409700</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>5908300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>6270200</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>6188900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AM21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2144,8 +2185,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2222,8 +2263,11 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2254,86 +2298,89 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3">
         <v>4225500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2236000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>461400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1468000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5188500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2671800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3437400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1301300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2160400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1514300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-835600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-275500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2904500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1749300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3202200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1312200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3419800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2364,86 +2411,89 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>911600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>398800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>718100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>361300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1094900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>752800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>726800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>299400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>590500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>484700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>667600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-51900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>722600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>476500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>758800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>305000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>637600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>597000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>840000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>406300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>515000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>775300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>456600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,8 +2602,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2584,86 +2637,89 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>3313900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1837200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-256800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1106700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4093600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1919000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2710600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1001900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1569900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1029600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-223600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2181900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1272800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2443400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1007200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2782200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2694,86 +2750,89 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3">
         <v>2433400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1426500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>763800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3368300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1584100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2056800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>708900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1038300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>762900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-547600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1346000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>825600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1627000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>623200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1915100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>821300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>885300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>939100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>727800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2941,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2914,8 +2976,8 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2992,8 +3054,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3167,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,8 +3280,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3244,86 +3315,89 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>2102200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>5502500</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>703600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>1411400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>1628800</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>4509800</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2833300</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2670400</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>2423800</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AL32" s="3" t="s">
+      <c r="AM32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3354,86 +3428,89 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3">
         <v>2433400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1426500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>763800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3368300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1584100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2056800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>708900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1038300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>762900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-547600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1346000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>825600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1627000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>623200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1915100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>821300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>885300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>939100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>727800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,8 +3619,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3574,201 +3654,207 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3">
         <v>2433400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1426500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>763800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3368300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1584100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2056800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>708900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1038300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>762900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-547600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1346000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>825600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1627000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>623200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1915100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>821300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>885300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>939100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>727800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3893,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,261 +3934,268 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>183626200</v>
-      </c>
-      <c r="E41" s="3">
+        <v>226473300</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3">
         <v>254869000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>222105700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>285282300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>234898000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>290533900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>247675700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>280915900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>242447800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>360815100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>301050600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>259139700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>330465000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>244721500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>261336700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>217609400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>254792900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>209707300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>225571000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>202919100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>220891500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>163996600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>194104600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>171349700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>197168400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>164605300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>601696900</v>
+        <v>584486200</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>435670400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>598030300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>490460700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>582460900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>454422500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>550563100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>498040400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>568965700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>568974100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>55417200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>494726400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>36272600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>427770700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>35223200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>530635700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>34644200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>467173200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>38143900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>525051700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>37311100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>529056200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>42058800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>579304100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>31521100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>513271000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>103433900</v>
-      </c>
-      <c r="E43" s="3">
+        <v>17832100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>15679700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102261900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18892100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>94427700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16369000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>97063900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16064400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4796800</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4177,8 +4271,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4209,8 +4306,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4287,41 +4384,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3146300</v>
-      </c>
-      <c r="E45" s="3">
+        <v>66637700</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>110808600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44546100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>91860100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30835000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>82510200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1684000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>81909400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1140800</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4397,41 +4497,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1375923000</v>
-      </c>
-      <c r="E46" s="3">
+        <v>897805000</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3">
         <v>817027600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>966944000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>888550300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>942621600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>843835500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>896986700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>878956300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>817351200</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4507,338 +4610,350 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>152276300</v>
-      </c>
-      <c r="E47" s="3">
+        <v>322517900</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
         <v>257400400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>138397300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>259011000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>127583300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>256665200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>124050600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>242974900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>131510200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>161700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>124300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>120800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>124800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>103000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>102300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>101600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>109000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>99700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>103800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>115600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>129800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>130700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>317300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>285900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>311000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>294500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>737700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>719200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>768600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>785400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>897600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>817900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>66201900</v>
-      </c>
-      <c r="E48" s="3">
+        <v>66257200</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>59330200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68001300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>61329700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65732000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>62352200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>62453400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>62811100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37437000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37611900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35715000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>35488400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34870800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34656500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>33577700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>32571600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>32128300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30009800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>30711500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>32522200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>34099900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33024900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>36724000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>31480500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>34927800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>31643800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5496100</v>
-      </c>
-      <c r="E49" s="3">
+        <v>9893100</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3">
         <v>8778300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5611200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9068900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5336100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9407500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5553600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6029500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4111300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4187800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4100200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4128300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4056800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4055600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="S49" s="3">
-        <v>4042600</v>
       </c>
       <c r="T49" s="3">
         <v>4042600</v>
       </c>
       <c r="U49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="V49" s="3">
         <v>4033500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4199300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4412700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5337300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8160200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5747700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8087800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5457100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5502900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5062,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,118 +5175,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>80158900</v>
-      </c>
-      <c r="E52" s="3">
+        <v>12400500</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
         <v>7712000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>84721200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9631400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>79254500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6109200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>87563500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8104800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>74657800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10223100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4869600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4209900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5059400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4181400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5058200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4621300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5898400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4095300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8964300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8922600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10436300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10796200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12949400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16134300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20145200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22854800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5401,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1680056200</v>
-      </c>
-      <c r="E54" s="3">
+        <v>1822068100</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3">
         <v>1629097200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1761752200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1705929500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1716000600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1717746200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1692894800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1723176900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1687987800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1644675200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5557,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,168 +5598,172 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>563273900</v>
-      </c>
-      <c r="E57" s="3">
+        <v>693417500</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3">
         <v>635552300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>586772300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>670938600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>572820200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>712377600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>575697500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>713595000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>582603200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24631900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>23345000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3">
         <v>21322900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3">
         <v>19225900</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3">
         <v>22898200</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="3">
         <v>25886100</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="3">
         <v>30259400</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>26338500</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AL57" s="3" t="s">
+      <c r="AM57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20018400</v>
-      </c>
-      <c r="E58" s="3">
+        <v>180716400</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3">
         <v>216699500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21950700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>141919000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23454500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>209366600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>464061200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>385420300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>48867900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>76110900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3">
         <v>121369300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5687,151 +5822,157 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5254000</v>
-      </c>
-      <c r="E59" s="3">
+        <v>236277200</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>231331400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36045100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>238126000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22035800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>228724400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4253800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3342800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2184900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2890800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>2985600</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>3007900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>2016700</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>1815300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
         <v>2759800</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>2592800</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2834200</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AL59" s="3" t="s">
+      <c r="AM59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>588546300</v>
-      </c>
-      <c r="E60" s="3">
+        <v>1117048700</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3">
         <v>1088663400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>644768000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1058070300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>618310500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1156958100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1044012500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1108622300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>633656000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5907,228 +6048,237 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>293265200</v>
+        <v>200932500</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>118668600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>317089000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>191327500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>318936200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>125073500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>304189200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>182185600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>308690800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45062700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>154313200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>41412000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>164361200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>56119500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>160479600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>53062900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>173731000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>54638600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>166334900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>59718600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>187453200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>61859900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>177461900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>43963200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>168898700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>54097600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>711705600</v>
-      </c>
-      <c r="E62" s="3">
+        <v>407579600</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3">
         <v>334438300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>713747500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>369303500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>694836600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>345750000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>261863900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>341551300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>663752700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12209100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7178000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7097700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7302100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6968600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6783400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5772400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6505600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5943500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6783700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7107300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6967700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8322500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12323400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15154400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>17011200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>19181900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6387,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6500,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6613,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1593517100</v>
-      </c>
-      <c r="E66" s="3">
+        <v>1731098100</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3">
         <v>1546699500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1675604500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1624056600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1632083300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1633467400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1610065600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1638041500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1606099500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1570499300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6769,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6880,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,8 +6993,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6937,8 +7106,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7219,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>42662100</v>
-      </c>
-      <c r="E72" s="3">
+        <v>46743400</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>39406800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>41528000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>38572800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>38705400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39111300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>38585900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>39577500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40320500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>78399300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38343200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>37034600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40266500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39322500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37390000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>35140400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>34342700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>31761200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>32832900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33673100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36431500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38298100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39706800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>37388300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>39071500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>38096500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AL72" s="3" t="s">
+      <c r="AM72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7445,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7558,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7671,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>76260300</v>
-      </c>
-      <c r="E76" s="3">
+        <v>80203200</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="3">
         <v>72736300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>75224200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>71605100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72652900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>72924700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>72054400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74243400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>74692500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>74176000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71662300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>70271700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>71449400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>70539100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>68531800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>66797900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>66569400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>61549600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>62889500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>66173500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>70660200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>74162100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>78050200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>73515600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>73961000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>72187700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,123 +7897,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7854,86 +8050,89 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3">
         <v>2433400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1426500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>763800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3368300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1584100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2056800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>708900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1038300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>762900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-547600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1346000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>825600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1627000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>623200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1915100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>821300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>885300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>939100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>727800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,8 +8171,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8004,86 +8204,89 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>5935600</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>5901800</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
         <v>5249300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
         <v>3003700</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3">
         <v>3068100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2769200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AL83" s="3" t="s">
+      <c r="AM83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8395,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8508,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8621,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8734,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,8 +8847,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8664,86 +8882,89 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>43298300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>22772600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>80580900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>8778900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
         <v>3392700</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>21205800</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AM89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,8 +9003,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8814,86 +9036,89 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AL91" s="3" t="s">
+      <c r="AM91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9227,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,8 +9340,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9144,86 +9375,89 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>-9969500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AL94" s="3" t="s">
+      <c r="AM94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,8 +9496,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9294,8 +9529,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9337,11 +9572,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -9349,11 +9584,11 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -9361,19 +9596,22 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9720,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9833,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,8 +9946,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9734,86 +9981,89 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>-237000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>2160400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>178600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
         <v>2184600</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-900200</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AM100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9844,68 +10094,68 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3">
         <v>2607300</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
         <v>2335200</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>778700</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB101" s="3">
         <v>845800</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
         <v>947500</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>0</v>
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH101" s="3">
         <v>0</v>
@@ -9922,8 +10172,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9954,82 +10207,85 @@
       <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3">
         <v>35686900</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>9436000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>73274000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>4652100</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
         <v>3339800</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>14449100</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AM102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,143 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,86 +832,89 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>19131600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>14651300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>11756000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>10311300</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>9862300</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>11817800</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>13838500</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>13949800</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>13909700</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AL8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM8" s="3">
+      <c r="AM8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AN8" s="3" t="s">
+      <c r="AO8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1023,8 +1029,11 @@
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1148,11 @@
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,8 +1429,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1451,8 +1470,8 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1529,8 +1548,11 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1567,86 +1589,89 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>-885000</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>-837800</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3">
         <v>-921500</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>-841100</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>-854800</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-814900</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-889600</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-852900</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-611600</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AN15" s="3" t="s">
+      <c r="AO15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,8 +1709,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1722,86 +1748,89 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3">
         <v>12803900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>492800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8687400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>608700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5863900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>211100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5462500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>292000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6073200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>537600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8143600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>925900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8100700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>403000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8077200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>315800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8066200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>292400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>228400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>574500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>736000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1838,86 +1867,89 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>6327700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>5963900</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>5892100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>4848800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>3789100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>3674200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>5737800</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5872600</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>5843500</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AO18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +1990,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1996,86 +2029,89 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>-2102200</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-703600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AO20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2112,86 +2148,89 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>10142300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>11090300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>7409700</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3">
         <v>5908300</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>6270200</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>6188900</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AO21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2228,8 +2267,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2306,8 +2345,11 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2344,86 +2386,89 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3">
         <v>4225500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2236000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>461400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1468000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5188500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2671800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3437400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1301300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2160400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1514300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-835600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-275500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2904500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1749300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3202200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1312200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3419800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2460,86 +2505,89 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3">
         <v>911600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>398800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>718100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>361300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1094900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>752800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>726800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>299400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>590500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>484700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>667600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-51900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>722600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>476500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>758800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>305000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>637600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>597000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>840000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>406300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>515000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>775300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>456600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,8 +2702,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2692,86 +2743,89 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3">
         <v>3313900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1837200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-256800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1106700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4093600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1919000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2710600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1001900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1569900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1029600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-223600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2181900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1272800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2443400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1007200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2782200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2808,86 +2862,89 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3">
         <v>2433400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1426500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>763800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3368300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1584100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2056800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>708900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1038300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>762900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-547600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1346000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>825600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1627000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>623200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1915100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>821300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>885300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>939100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>727800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3040,8 +3100,8 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,8 +3416,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3388,86 +3457,89 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>2102200</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>5502500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>703600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>1411400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>1628800</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>4509800</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2833300</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>2670400</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>2423800</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AO32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3504,86 +3576,89 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3">
         <v>2433400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1426500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>763800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3368300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1584100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2056800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>708900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1038300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>762900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-547600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1346000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>825600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1627000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>623200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1915100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>821300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>885300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>939100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>727800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,8 +3773,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3736,207 +3814,213 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3">
         <v>2433400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1426500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>763800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3368300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1584100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2056800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>708900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1038300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>762900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-547600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1346000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>825600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1627000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>623200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1915100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>821300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>885300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>939100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>727800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,279 +4104,286 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>209342500</v>
+      </c>
+      <c r="E41" s="3">
         <v>192419300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>226473300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>183626200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>254869000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>222105700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>285282300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>234898000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>290533900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>247675700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>280915900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>242447800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>360815100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>301050600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>259139700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>330465000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>244721500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>261336700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>217609400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>254792900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>209707300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>225571000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>202919100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>220891500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>163996600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>194104600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>171349700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>197168400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>164605300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>530510700</v>
+      </c>
+      <c r="E42" s="3">
         <v>710691100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>584486200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>601696900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>435670400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>598030300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>490460700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>582460900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>454422500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>550563100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>498040400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>568965700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>568974100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>55417200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>494726400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>36272600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>427770700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>35223200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>530635700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>34644200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>467173200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>38143900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>525051700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>37311100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>529056200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>42058800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>579304100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>31521100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>513271000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20861800</v>
+      </c>
+      <c r="E43" s="3">
         <v>4764800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17832100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>103433900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15679700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5058000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18892100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>94427700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16369000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>97063900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16064400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4796800</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4367,8 +4459,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4405,8 +4500,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4483,47 +4578,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>96528100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3465900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>66637700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3146300</v>
       </c>
-      <c r="G45" s="3">
-        <v>110808600</v>
-      </c>
       <c r="H45" s="3">
+        <v>108953300</v>
+      </c>
+      <c r="I45" s="3">
         <v>44546100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>91860100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30835000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>82510200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1684000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>81909400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1140800</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4599,47 +4697,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>859424700</v>
+      </c>
+      <c r="E46" s="3">
         <v>911341100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>897805000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>891903400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>817027600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>869740100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>888550300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>942621600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>843835500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>896986700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>878956300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>817351200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4715,356 +4816,368 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>342381100</v>
+      </c>
+      <c r="E47" s="3">
         <v>182785400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>322517900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>152276300</v>
       </c>
-      <c r="G47" s="3">
-        <v>257400400</v>
-      </c>
       <c r="H47" s="3">
+        <v>278598200</v>
+      </c>
+      <c r="I47" s="3">
         <v>138397300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>259011000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>127583300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>256665200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>124050600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>242974900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>131510200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>161700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>124300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>120800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>124800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>103000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>102300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>101600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>109000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>99700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>103800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>115600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>129800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>130700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>317300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>285900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>311000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>294500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>737700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>719200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>768600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>785400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>897600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>817900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>66524600</v>
+      </c>
+      <c r="E48" s="3">
         <v>70582000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>66257200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>66201900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>59330200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>68001300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>61329700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>65732000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>62352200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62453400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62811100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37437000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37611900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35715000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35488400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34870800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34656500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>33577700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>32571600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>32128300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>30009800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>30711500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>32522200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>34099900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>33024900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>36724000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>31480500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>34927800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31643800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9687700</v>
+      </c>
+      <c r="E49" s="3">
         <v>5965000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9893100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5496100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8778300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5611200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9068900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5336100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9407500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5553600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6029500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4111300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4187800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4100200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4128300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4056800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4055600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="U49" s="3">
-        <v>4042600</v>
       </c>
       <c r="V49" s="3">
         <v>4042600</v>
       </c>
       <c r="W49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="X49" s="3">
         <v>4033500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4199300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4412700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5337300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8160200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5747700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8087800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5457100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5502900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,124 +5411,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11957300</v>
+      </c>
+      <c r="E52" s="3">
         <v>88335100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12400500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>80158900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7712000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>84721200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9631400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>79254500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6109200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>87563500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8104800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>74657800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10223100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4869600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4209900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5059400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4181400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5058200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4621300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5898400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4095300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8964300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8922600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10436300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10796200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>12949400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>16134300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20145200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>22854800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1815945800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1873436600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1822068100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1680056200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1629097200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1761752200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1705929500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1716000600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1717746200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1692894800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1723176900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1687987800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1644675200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,180 +5856,184 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>715560600</v>
+      </c>
+      <c r="E57" s="3">
         <v>620336700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>693417500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>563273900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>635552300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>586772300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>670938600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>572820200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>712377600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>575697500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>713595000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>582603200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24631900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3">
         <v>23345000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3">
         <v>21322900</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3">
         <v>19225900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="3">
         <v>22898200</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="3">
         <v>25886100</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>30259400</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
         <v>26338500</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AN57" s="3" t="s">
+      <c r="AO57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>232464500</v>
+      </c>
+      <c r="E58" s="3">
         <v>20646500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>180716400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20018400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>216699500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21950700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>141919000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23454500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>209366600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>464061200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>385420300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>48867900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>76110900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T58" s="3">
         <v>121369300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5959,163 +6092,169 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11947900</v>
+      </c>
+      <c r="E59" s="3">
         <v>5823100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>236277200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5254000</v>
       </c>
-      <c r="G59" s="3">
-        <v>231331400</v>
-      </c>
       <c r="H59" s="3">
+        <v>34103900</v>
+      </c>
+      <c r="I59" s="3">
         <v>36045100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>238126000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22035800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>228724400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4253800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3342800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2184900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2890800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>2985600</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>3007900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>2016700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1815300</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>2759800</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2592800</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2834200</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AO59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>966609100</v>
+      </c>
+      <c r="E60" s="3">
         <v>646806300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1117048700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>588546300</v>
       </c>
-      <c r="G60" s="3">
-        <v>1088663400</v>
-      </c>
       <c r="H60" s="3">
+        <v>891436000</v>
+      </c>
+      <c r="I60" s="3">
         <v>644768000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1058070300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>618310500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1156958100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1044012500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1108622300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>633656000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6191,240 +6330,249 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>123166600</v>
+      </c>
+      <c r="E61" s="3">
         <v>319669100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200932500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>293265200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>118668600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>317089000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>191327500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>318936200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>125073500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>304189200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>182185600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>308690800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45062700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>154313200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>41412000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>164361200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>56119500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>160479600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>53062900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>173731000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>54638600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>166334900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>59718600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>187453200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>61859900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>177461900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>43963200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>168898700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>54097600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>627177400</v>
+      </c>
+      <c r="E62" s="3">
         <v>813720500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>407579600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>711705600</v>
       </c>
-      <c r="G62" s="3">
-        <v>334438300</v>
-      </c>
       <c r="H62" s="3">
+        <v>531665800</v>
+      </c>
+      <c r="I62" s="3">
         <v>713747500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>369303500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>694836600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>345750000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>261863900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>341551300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>663752700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12209100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7178000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7097700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7302100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6968600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6783400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5772400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6505600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5943500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6783700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7107300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6967700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8322500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12323400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>15154400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17011200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>19181900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1722571300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1780195900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1731098100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1593517100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1546699500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1675604500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1624056600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1632083300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1633467400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1610065600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1638041500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1606099500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1570499300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>49153500</v>
+      </c>
+      <c r="E72" s="3">
         <v>47804800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>46743400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>42662100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>39406800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>41528000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>38572800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>38705400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>39111300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38585900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>39577500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40320500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>78399300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38343200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>37034600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>40266500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>39322500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37390000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>35140400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>34342700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31761200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>32832900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33673100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36431500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>38298100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>39706800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>37388300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>39071500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>38096500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AN72" s="3" t="s">
+      <c r="AO72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>82357600</v>
+      </c>
+      <c r="E76" s="3">
         <v>81926600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>80203200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>76260300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72736300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>75224200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>71605100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>72652900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>72924700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>72054400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>74243400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74692500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>74176000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>71662300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>70271700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71449400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70539100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>68531800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>66797900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>66569400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61549600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>62889500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>66173500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>70660200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>74162100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>78050200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>73515600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>73961000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>72187700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,129 +8277,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8248,86 +8442,89 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3">
         <v>2433400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1426500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>763800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3368300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1584100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2056800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>708900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1038300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>762900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-547600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1346000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>825600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1627000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>623200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1915100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>821300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>885300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>939100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>727800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,8 +8565,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8406,86 +8604,89 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
         <v>5935600</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
         <v>5901800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
         <v>5249300</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3">
         <v>3003700</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>3068100</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2769200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AO83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,8 +9277,11 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9102,86 +9318,89 @@
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>43298300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>22772600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X89" s="3">
         <v>80580900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
         <v>8778900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>3392700</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>21205800</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AO89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,8 +9441,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9260,86 +9480,89 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AO91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,8 +9796,11 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9608,86 +9837,89 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3">
         <v>-9969500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AO94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,8 +9960,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9766,8 +9999,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9809,11 +10042,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -9821,11 +10054,11 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -9833,19 +10066,22 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,8 +10434,11 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10230,86 +10475,89 @@
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3">
         <v>-237000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X100" s="3">
         <v>2160400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
         <v>178600</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>2184600</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-900200</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AO100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10346,68 +10594,68 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3">
         <v>2607300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3">
         <v>2335200</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB101" s="3">
         <v>778700</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
         <v>845800</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3">
         <v>947500</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>0</v>
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ101" s="3">
         <v>0</v>
@@ -10424,8 +10672,11 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10462,82 +10713,85 @@
       <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3">
         <v>35686900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>9436000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3">
         <v>73274000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
         <v>4652100</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>3339800</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>14449100</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AO102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,146 +656,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,86 +838,89 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3">
         <v>19131600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>14651300</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
         <v>11756000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W8" s="3">
         <v>10311300</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="3">
         <v>9862300</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="3">
         <v>11817800</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3">
         <v>13838500</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="3">
         <v>13949800</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
         <v>13909700</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AI8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="3">
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AK8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL8" s="3">
+      <c r="AL8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AM8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN8" s="3">
+      <c r="AN8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AO8" s="3" t="s">
+      <c r="AP8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1032,8 +1038,11 @@
       <c r="AO9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,8 +1160,11 @@
       <c r="AO10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,8 +1448,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1473,8 +1492,8 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1551,8 +1570,11 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1592,86 +1614,89 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-885000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3">
         <v>-837800</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15" s="3">
         <v>-921500</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W15" s="3">
         <v>-841100</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-854800</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="3">
         <v>-814900</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-889600</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-852900</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-611600</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL15" s="3">
+      <c r="AL15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AM15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN15" s="3">
+      <c r="AN15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AO15" s="3" t="s">
+      <c r="AP15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,8 +1735,9 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1751,86 +1777,89 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3">
         <v>12803900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>492800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8687400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>608700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5863900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>211100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5462500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>292000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6073200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>537600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8143600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>925900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8100700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>403000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8077200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>315800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8066200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>292400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>228400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>574500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>736000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1870,86 +1899,89 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>6327700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>5963900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>5892100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>4848800</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>3789100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3">
         <v>3674200</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3">
         <v>5737800</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="3">
         <v>5872600</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>5843500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AL18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AM18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN18" s="3">
+      <c r="AN18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AO18" s="3" t="s">
+      <c r="AP18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,8 +2023,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,86 +2065,89 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-2102200</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>-703600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AL20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AM20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN20" s="3">
+      <c r="AN20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AO20" s="3" t="s">
+      <c r="AP20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2151,86 +2187,89 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>10142300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>11090300</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>7409700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3">
         <v>5908300</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>6270200</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>6188900</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AO21" s="3" t="s">
+      <c r="AP21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2270,8 +2309,8 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2348,8 +2387,11 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2389,86 +2431,89 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3">
         <v>4225500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2236000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>461400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1468000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5188500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2671800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3437400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1301300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2160400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1514300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-835600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-275500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2904500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1749300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3202200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1312200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3419800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2508,86 +2553,89 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
         <v>911600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>398800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>718100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>361300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1094900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>752800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>726800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>299400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>590500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>484700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>667600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-51900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>722600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>476500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>758800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>305000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>637600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>597000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>840000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>406300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>515000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>775300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>456600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,8 +2753,11 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2746,86 +2797,89 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3">
         <v>3313900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1837200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-256800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1106700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4093600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1919000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2710600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1001900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1569900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1029600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-223600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2181900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1272800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2443400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1007200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2782200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2865,86 +2919,89 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3">
         <v>2433400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1426500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>763800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3368300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1584100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2056800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>708900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1038300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>762900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-547600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1346000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>825600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1627000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>623200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1915100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>821300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>885300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>939100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>727800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3103,8 +3163,8 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -3181,8 +3241,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,8 +3485,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3460,86 +3529,89 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>2102200</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>5502500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>703600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>1411400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1628800</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="3">
         <v>4509800</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="3">
         <v>2833300</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="3">
         <v>2670400</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>2423800</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AL32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AM32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN32" s="3">
+      <c r="AN32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AO32" s="3" t="s">
+      <c r="AP32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3579,86 +3651,89 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3">
         <v>2433400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1426500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>763800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3368300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1584100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2056800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>708900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1038300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>762900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-547600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1346000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>825600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1627000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>623200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1915100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>821300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>885300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>939100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>727800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,8 +3851,11 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3817,210 +3895,216 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3">
         <v>2433400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1426500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>763800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3368300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1584100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2056800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>708900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1038300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>762900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-547600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1346000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>825600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1627000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>623200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1915100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>821300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>885300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>939100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>727800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,288 +4190,295 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>178238200</v>
+      </c>
+      <c r="E41" s="3">
         <v>209342500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>192419300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>226473300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>183626200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>254869000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>222105700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>285282300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>234898000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>290533900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>247675700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>280915900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>242447800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>360815100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>301050600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>259139700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>330465000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>244721500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>261336700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>217609400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>254792900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>209707300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>225571000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>202919100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>220891500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>163996600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>194104600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171349700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>197168400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>164605300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>699131800</v>
+      </c>
+      <c r="E42" s="3">
         <v>530510700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>710691100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>584486200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>601696900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>435670400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>598030300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>490460700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>582460900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>454422500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>550563100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>498040400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>568965700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>568974100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>55417200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>494726400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>36272600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>427770700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>35223200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>530635700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>34644200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>467173200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>38143900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>525051700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>37311100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>529056200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>42058800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>579304100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>31521100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>513271000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4972900</v>
+      </c>
+      <c r="E43" s="3">
         <v>20861800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4764800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17832100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>103433900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15679700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5058000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18892100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>94427700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16369000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>97063900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16064400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4796800</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4462,8 +4554,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4503,8 +4598,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4581,50 +4676,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3120000</v>
+      </c>
+      <c r="E45" s="3">
         <v>96528100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3465900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>66637700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3146300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>108953300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44546100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>91860100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30835000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>82510200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1684000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>81909400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1140800</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4700,50 +4798,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>885462900</v>
+      </c>
+      <c r="E46" s="3">
         <v>859424700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>911341100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>897805000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>891903400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>817027600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>869740100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>888550300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>942621600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>843835500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>896986700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>878956300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>817351200</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4819,365 +4920,377 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>183879900</v>
+      </c>
+      <c r="E47" s="3">
         <v>342381100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>182785400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>322517900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>152276300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>278598200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>138397300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>259011000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>127583300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>256665200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>124050600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>242974900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>131510200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>161700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>124300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>120800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>124800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>103000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>102300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>101600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>109000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>99700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>103800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>115600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>129800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>130700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>317300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>285900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>311000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>294500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>737700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>719200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>768600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>785400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>897600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>817900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69184800</v>
+      </c>
+      <c r="E48" s="3">
         <v>66524600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>70582000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>66257200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66201900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>59330200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>68001300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>61329700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>65732000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62352200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62453400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>62811100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37437000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37611900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35715000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35488400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34870800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34656500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>33577700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>32571600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>32128300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>30009800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>30711500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>32522200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>34099900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>33024900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>36724000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>31480500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>34927800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31643800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6036000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9687700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5965000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9893100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5496100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8778300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5611200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9068900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5336100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9407500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5553600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6029500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4111300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4187800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4100200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4128300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4056800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4055600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="V49" s="3">
-        <v>4042600</v>
       </c>
       <c r="W49" s="3">
         <v>4042600</v>
       </c>
       <c r="X49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="Y49" s="3">
         <v>4033500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4199300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4412700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5337300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8160200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5747700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8087800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5457100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5502900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5530,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>97901500</v>
+      </c>
+      <c r="E52" s="3">
         <v>11957300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>88335100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12400500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>80158900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7712000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>84721200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9631400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>79254500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6109200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>87563500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8104800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>74657800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10223100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4869600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4209900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5059400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4181400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5058200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4621300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5898400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4095300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8964300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8922600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10436300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10796200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12949400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16134300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20145200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>22854800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1875887200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1815945800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1873436600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1822068100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1680056200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1629097200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1761752200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1705929500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1716000600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1717746200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1692894800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1723176900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1687987800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1644675200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,186 +5986,190 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>621238300</v>
+      </c>
+      <c r="E57" s="3">
         <v>715560600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>620336700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>693417500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>563273900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>635552300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>586772300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>670938600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>572820200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>712377600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>575697500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>713595000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>582603200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24631900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3">
         <v>23345000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W57" s="3">
         <v>21322900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y57" s="3">
         <v>19225900</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA57" s="3">
         <v>22898200</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC57" s="3">
         <v>25886100</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE57" s="3">
         <v>30259400</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG57" s="3">
         <v>26338500</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL57" s="3">
+      <c r="AL57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AM57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN57" s="3">
+      <c r="AN57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AO57" s="3" t="s">
+      <c r="AP57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22627700</v>
+      </c>
+      <c r="E58" s="3">
         <v>232464500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20646500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>180716400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20018400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>216699500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21950700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>141919000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23454500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>209366600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>464061200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>385420300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>48867900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>76110900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3">
         <v>121369300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -6095,169 +6228,175 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6670100</v>
+      </c>
+      <c r="E59" s="3">
         <v>11947900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5823100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>236277200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5254000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34103900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>36045100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>238126000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22035800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>228724400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4253800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3342800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2184900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2890800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3">
         <v>2985600</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
         <v>3007900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3">
         <v>2016700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1815300</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3">
         <v>2759800</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE59" s="3">
         <v>2592800</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG59" s="3">
         <v>2834200</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL59" s="3">
+      <c r="AL59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AM59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN59" s="3">
+      <c r="AN59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AO59" s="3" t="s">
+      <c r="AP59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>650536100</v>
+      </c>
+      <c r="E60" s="3">
         <v>966609100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>646806300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1117048700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>588546300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>891436000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>644768000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1058070300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>618310500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1156958100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1044012500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1108622300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>633656000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6333,246 +6472,255 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>321565800</v>
+      </c>
+      <c r="E61" s="3">
         <v>123166600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>319669100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>200932500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>293265200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>118668600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>317089000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>191327500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>318936200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>125073500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>304189200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>182185600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>308690800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45062700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>154313200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>41412000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>164361200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>56119500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>160479600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>53062900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>173731000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>54638600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>166334900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>59718600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>187453200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>61859900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>177461900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>43963200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>168898700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>54097600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>811124200</v>
+      </c>
+      <c r="E62" s="3">
         <v>627177400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>813720500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>407579600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>711705600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>531665800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>713747500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>369303500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>694836600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>345750000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>261863900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>341551300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>663752700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12209100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7178000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7097700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7302100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6968600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6783400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5772400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6505600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5943500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6783700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7107300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6967700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8322500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12323400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>15154400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17011200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19181900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1783226100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1722571300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1780195900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1731098100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1593517100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1546699500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1675604500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1624056600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1632083300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1633467400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1610065600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1638041500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1606099500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1570499300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7492,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>49834000</v>
+      </c>
+      <c r="E72" s="3">
         <v>49153500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>47804800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>46743400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>42662100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>39406800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>41528000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>38572800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>38705400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>39111300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38585900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>39577500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40320500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78399300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38343200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37034600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40266500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>39322500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37390000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>35140400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>34342700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31761200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>32832900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>33673100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>36431500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>38298100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>39706800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>37388300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>39071500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>38096500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL72" s="3">
+      <c r="AL72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN72" s="3">
+      <c r="AN72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AO72" s="3" t="s">
+      <c r="AP72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>81859800</v>
+      </c>
+      <c r="E76" s="3">
         <v>82357600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>81926600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>80203200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>76260300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72736300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>75224200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71605100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>72652900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>72924700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>72054400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74243400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>74692500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>74176000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71662300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>70271700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>71449400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>70539100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>68531800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>66797900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>66569400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>61549600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>62889500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>66173500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>70660200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>74162100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>78050200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>73515600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>73961000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>72187700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,132 +8468,138 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8445,86 +8639,89 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3">
         <v>2433400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1426500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>763800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3368300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1584100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2056800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>708900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1038300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>762900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-547600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1346000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>825600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1627000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>623200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1915100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>821300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>885300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>939100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>727800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,8 +8763,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8607,86 +8805,89 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5935600</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3">
         <v>5901800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
         <v>5249300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC83" s="3">
         <v>3003700</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE83" s="3">
         <v>3068100</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG83" s="3">
         <v>2769200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL83" s="3">
+      <c r="AL83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN83" s="3">
+      <c r="AN83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AO83" s="3" t="s">
+      <c r="AP83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,8 +9493,11 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9321,86 +9537,89 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
         <v>43298300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3">
         <v>22772600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y89" s="3">
         <v>80580900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC89" s="3">
         <v>8778900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE89" s="3">
         <v>3392700</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG89" s="3">
         <v>21205800</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AL89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN89" s="3">
+      <c r="AN89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AO89" s="3" t="s">
+      <c r="AP89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,8 +9661,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9483,86 +9703,89 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL91" s="3">
+      <c r="AL91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AM91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN91" s="3">
+      <c r="AN91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AO91" s="3" t="s">
+      <c r="AP91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,8 +10025,11 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9840,86 +10069,89 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-9969500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AL94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN94" s="3">
+      <c r="AN94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AO94" s="3" t="s">
+      <c r="AP94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,8 +10193,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10002,8 +10235,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10045,11 +10278,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -10057,11 +10290,11 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -10069,19 +10302,22 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,8 +10679,11 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10478,86 +10723,89 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-237000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3">
         <v>2160400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC100" s="3">
         <v>178600</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3">
         <v>2184600</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-900200</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AL100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN100" s="3">
+      <c r="AN100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AO100" s="3" t="s">
+      <c r="AP100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,68 +10845,68 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3">
         <v>2607300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U101" s="3">
         <v>2335200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC101" s="3">
         <v>778700</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE101" s="3">
         <v>845800</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG101" s="3">
         <v>947500</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
+      <c r="AJ101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK101" s="3">
         <v>0</v>
@@ -10675,8 +10923,11 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10716,82 +10967,85 @@
       <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3">
         <v>35686900</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3">
         <v>9436000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3">
         <v>73274000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC102" s="3">
         <v>4652100</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE102" s="3">
         <v>3339800</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG102" s="3">
         <v>14449100</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AL102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN102" s="3">
+      <c r="AN102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AO102" s="3" t="s">
+      <c r="AP102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
